--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -11,8 +11,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックリスト" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$31</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$23</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$35</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -572,7 +572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C22"/>
+  <dimension ref="A1:C23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -626,7 +626,7 @@
           <t>・始める前に、洗濯機横のフィルター2か所と乾燥フィルターにゴミがないか確認し、たまっていれば取る
 ・洗濯機を回す
 ・乾燥機にかけるもの：タオル、靴下など
-・乾燥機にかけないもの：ボクサーパンツ、その他の衣類（干す）
+・乾燥機にかけないもの：ボクサーパンツ（必ず干す）、その他の衣類
 ※洗濯機のフタが壊れています。開け閉めはゆっくり注意して行ってください</t>
         </is>
       </c>
@@ -649,7 +649,7 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="92" customHeight="1">
+    <row r="8" ht="106" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>3</v>
       </c>
@@ -664,7 +664,7 @@
 ・プロテインシェイカーは、こびり付いていることがあるので、スポンジでこすって泡を流してから食洗機へ
 ・ガスコンロと天板を掃除する
 ・排水口のゴミを取って捨てる（対象の週はここでパイプユニッシュを入れる）
-・シンクは最後に乾拭きする</t>
+・シンクは最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）</t>
         </is>
       </c>
     </row>
@@ -711,7 +711,7 @@
         <is>
           <t>・ボウルをこすって掃除する
 ・排水口のゴミ・髪の毛を取って掃除する
-・最後に乾拭きする
+・最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
 ・中央の鏡の中にあるゴミ箱の中身を捨てる（袋はそのまま。交換は月1回）</t>
         </is>
       </c>
@@ -737,7 +737,7 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="36" customHeight="1">
+    <row r="13" ht="42" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>8</v>
       </c>
@@ -748,8 +748,8 @@
       </c>
       <c r="C13" s="8" t="inlineStr">
         <is>
-          <t>・掃除機をかけてから、クイックルワイパー（ウエット）で拭く
-・時間が足りない日は掃除機だけで構いません</t>
+          <t>・毎回：掃除機をかける
+・2週に1回（対象の週）：掃除機のあと、クイックルワイパー（ウエット）で拭く</t>
         </is>
       </c>
     </row>
@@ -759,10 +759,27 @@
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
+          <t>靴磨き・消臭</t>
+        </is>
+      </c>
+      <c r="C14" s="8" t="inlineStr">
+        <is>
+          <t>・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
+・毎回：玄関の靴、カーテン、ソファなどの布製品に消臭スプレーをかける
+　（革製品・シルクなど、スプレーの表示で使えない素材にはかけない）</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="52" customHeight="1">
+      <c r="A15" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
           <t>洗濯物を干す</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C15" s="8" t="inlineStr">
         <is>
           <t>・横のカゴに入れてベランダへ持っていき、干す
 ・風が強い日は、竿の下のフックにかける
@@ -770,48 +787,48 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="34" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>洗濯機の後始末</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
-        </is>
-      </c>
-    </row>
     <row r="16" ht="34" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
       <c r="B16" s="7" t="inlineStr">
         <is>
+          <t>洗濯機の後始末</t>
+        </is>
+      </c>
+      <c r="C16" s="8" t="inlineStr">
+        <is>
+          <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="34" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
           <t>燃えるゴミ</t>
         </is>
       </c>
-      <c r="C16" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>・家中のゴミをまとめて出す（量が少なくても毎回。収集は14時ごろ）</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="8" customHeight="1"/>
-    <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="4" t="inlineStr">
+    <row r="18" ht="8" customHeight="1"/>
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="4" t="inlineStr">
         <is>
           <t>お風呂の防カビくん煙剤（2か月に1回）</t>
         </is>
       </c>
-      <c r="B18" s="5" t="n"/>
-      <c r="C18" s="5" t="n"/>
-    </row>
-    <row r="19" ht="66" customHeight="1">
-      <c r="A19" s="3" t="inlineStr">
+      <c r="B19" s="5" t="n"/>
+      <c r="C19" s="5" t="n"/>
+    </row>
+    <row r="20" ht="66" customHeight="1">
+      <c r="A20" s="3" t="inlineStr">
         <is>
           <t>・お風呂掃除が終わってからたく。シャンプー等の置き方、濡れたままでよいか、待ち時間は、製品の説明書きに従ってください
 ・たいている間は浴室のドア・窓を閉め、換気扇を止め、浴室に入らない
@@ -819,36 +836,36 @@
         </is>
       </c>
     </row>
-    <row r="20" ht="8" customHeight="1"/>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="4" t="inlineStr">
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="56" customHeight="1">
-      <c r="A22" s="9" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="56" customHeight="1">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>・パイプユニッシュ（塩素系）は、酸性の洗剤やクエン酸と絶対に混ぜない。使っている間は換気する
 ・高い所の作業や、無理な姿勢での作業はしなくて構いません
 ・気づいたこと、足りない洗剤などは、チェックリストの連絡事項に書いてください</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
     <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
+    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A18:C18"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
+    <mergeCell ref="A20:C20"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -863,7 +880,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F31"/>
+  <dimension ref="A1:F35"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="40" customWidth="1" min="1" max="1"/>
@@ -1060,7 +1077,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>床（掃除機→クイックルワイパー）</t>
+          <t>床の掃除機がけ</t>
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
@@ -1072,7 +1089,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>洗濯物を干す</t>
+          <t>消臭スプレー（靴・カーテン・ソファ等）</t>
         </is>
       </c>
       <c r="B16" s="14" t="n"/>
@@ -1084,7 +1101,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>洗濯機のフタを開けて乾かす</t>
+          <t>洗濯物を干す</t>
         </is>
       </c>
       <c r="B17" s="14" t="n"/>
@@ -1096,7 +1113,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>燃えるゴミ出し</t>
+          <t>洗濯機のフタを開けて乾かす</t>
         </is>
       </c>
       <c r="B18" s="14" t="n"/>
@@ -1105,82 +1122,82 @@
       <c r="E18" s="14" t="n"/>
       <c r="F18" s="14" t="n"/>
     </row>
-    <row r="19" ht="18" customHeight="1">
-      <c r="A19" s="13" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>燃えるゴミ出し</t>
+        </is>
+      </c>
+      <c r="B19" s="14" t="n"/>
+      <c r="C19" s="14" t="n"/>
+      <c r="D19" s="14" t="n"/>
+      <c r="E19" s="14" t="n"/>
+      <c r="F19" s="14" t="n"/>
+    </row>
+    <row r="20" ht="18" customHeight="1">
+      <c r="A20" s="13" t="inlineStr">
         <is>
           <t>【2週に1回】</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-      <c r="D19" s="5" t="n"/>
-      <c r="E19" s="5" t="n"/>
-      <c r="F19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>パイプユニッシュ（キッチン・お風呂）</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F20" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+      <c r="D20" s="5" t="n"/>
+      <c r="E20" s="5" t="n"/>
+      <c r="F20" s="5" t="n"/>
     </row>
     <row r="21" ht="22" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>パイプユニッシュ（キッチン・お風呂）</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F21" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>シーツ・枕カバーの洗濯</t>
         </is>
       </c>
-      <c r="B21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
-        <is>
-          <t>【月1回】</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="14" t="n"/>
+      <c r="D22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="14" t="n"/>
+      <c r="F22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>パイプユニッシュ（洗面台）</t>
+          <t>床のクイックルワイパー（ウエット）</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
@@ -1194,56 +1211,32 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="E23" s="14" t="n"/>
       <c r="F23" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+    <row r="24" ht="18" customHeight="1">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>【月1回】</t>
+        </is>
+      </c>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
+      <c r="D24" s="5" t="n"/>
+      <c r="E24" s="5" t="n"/>
+      <c r="F24" s="5" t="n"/>
     </row>
     <row r="25" ht="22" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
-          <t>洗面台ゴミ箱の袋交換</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+          <t>靴磨き（靴クリーム）</t>
+        </is>
+      </c>
+      <c r="B25" s="14" t="n"/>
       <c r="C25" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1254,29 +1247,49 @@
           <t>—</t>
         </is>
       </c>
-      <c r="E25" s="14" t="n"/>
+      <c r="E25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F25" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
-        <is>
-          <t>【2か月に1回（　　月・　　月・　　月…）】</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>パイプユニッシュ（洗面台）</t>
+        </is>
+      </c>
+      <c r="B26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="14" t="n"/>
+      <c r="D26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>お風呂の防カビくん煙剤（対象月のみ）</t>
+          <t>撥水コート（シンク・洗面台）</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
@@ -1289,46 +1302,78 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="14" t="n"/>
+      <c r="D27" s="14" t="n"/>
+      <c r="E27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F27" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>作業時間（開始〜終了）</t>
-        </is>
-      </c>
-      <c r="B28" s="5" t="n"/>
-      <c r="C28" s="5" t="n"/>
-      <c r="D28" s="5" t="n"/>
-      <c r="E28" s="5" t="n"/>
-      <c r="F28" s="5" t="n"/>
-    </row>
-    <row r="29" ht="26" customHeight="1">
-      <c r="A29" s="16" t="inlineStr">
-        <is>
-          <t>作業員サイン</t>
-        </is>
-      </c>
-      <c r="B29" s="5" t="n"/>
-      <c r="C29" s="5" t="n"/>
-      <c r="D29" s="5" t="n"/>
-      <c r="E29" s="5" t="n"/>
-      <c r="F29" s="5" t="n"/>
-    </row>
-    <row r="30" ht="70" customHeight="1">
-      <c r="A30" s="16" t="inlineStr">
-        <is>
-          <t>連絡事項</t>
+    <row r="28" ht="22" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
+        </is>
+      </c>
+      <c r="B28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E28" s="14" t="n"/>
+      <c r="F28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="29" ht="22" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>洗面台ゴミ箱の袋交換</t>
+        </is>
+      </c>
+      <c r="B29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="14" t="n"/>
+      <c r="F29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="18" customHeight="1">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>【2か月に1回（　　月・　　月・　　月…）】</t>
         </is>
       </c>
       <c r="B30" s="5" t="n"/>
@@ -1337,8 +1382,72 @@
       <c r="E30" s="5" t="n"/>
       <c r="F30" s="5" t="n"/>
     </row>
-    <row r="31">
-      <c r="A31" s="11" t="inlineStr">
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>お風呂の防カビくん煙剤（対象月のみ）</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="30" customHeight="1">
+      <c r="A32" s="16" t="inlineStr">
+        <is>
+          <t>作業時間（開始〜終了）</t>
+        </is>
+      </c>
+      <c r="B32" s="5" t="n"/>
+      <c r="C32" s="5" t="n"/>
+      <c r="D32" s="5" t="n"/>
+      <c r="E32" s="5" t="n"/>
+      <c r="F32" s="5" t="n"/>
+    </row>
+    <row r="33" ht="26" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
+        <is>
+          <t>作業員サイン</t>
+        </is>
+      </c>
+      <c r="B33" s="5" t="n"/>
+      <c r="C33" s="5" t="n"/>
+      <c r="D33" s="5" t="n"/>
+      <c r="E33" s="5" t="n"/>
+      <c r="F33" s="5" t="n"/>
+    </row>
+    <row r="34" ht="70" customHeight="1">
+      <c r="A34" s="16" t="inlineStr">
+        <is>
+          <t>連絡事項</t>
+        </is>
+      </c>
+      <c r="B34" s="5" t="n"/>
+      <c r="C34" s="5" t="n"/>
+      <c r="D34" s="5" t="n"/>
+      <c r="E34" s="5" t="n"/>
+      <c r="F34" s="5" t="n"/>
+    </row>
+    <row r="35">
+      <c r="A35" s="11" t="inlineStr">
         <is>
           <t>※第5月曜がない月は、第5月曜の欄は使いません。作業の詳しい手順は「作業手順書」を見てください。</t>
         </is>
@@ -1346,13 +1455,13 @@
     </row>
   </sheetData>
   <mergeCells count="7">
+    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:F31"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A20:F20"/>
+    <mergeCell ref="A30:F30"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -9,10 +9,12 @@
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="作業手順書" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="チェックリスト" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具・洗剤リスト" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$23</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$24</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'道具・洗剤リスト'!$A$1:$E$36</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -161,7 +163,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -206,6 +208,21 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -572,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -668,118 +685,136 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="34" customHeight="1">
+    <row r="9" ht="36" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>4</v>
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>ベッドメイキング</t>
+          <t>寝室</t>
         </is>
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>・シーツを整える。シーツ類を洗う週は、洗ったものに交換する</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1">
+          <t>・ベッドメイキング（シーツ類を洗う週は、洗ったものに交換する）
+・ベッドフレーム、ティッシュを置いている台のホコリを取る</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="44" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>5</v>
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>トイレ</t>
+          <t>テーブル</t>
         </is>
       </c>
       <c r="C10" s="8" t="inlineStr">
         <is>
-          <t>・トイレ掃除（掃除道具は上の棚にあります）</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="76" customHeight="1">
+          <t>・食卓のテーブル、仕事用のテーブル（ガラス）のホコリをハンディモップで取る
+・汚れている場合は、水拭き → 乾拭き</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>6</v>
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="C11" s="8" t="inlineStr">
+        <is>
+          <t>・トイレ掃除（掃除道具は上の棚にあります）</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="52" customHeight="1">
+      <c r="A12" s="6" t="n">
+        <v>7</v>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
           <t>洗面化粧台</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>・ボウルをこすって掃除する
 ・排水口のゴミ・髪の毛を取って掃除する
-・最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
-・中央の鏡の中にあるゴミ箱の中身を捨てる（袋はそのまま。交換は月1回）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="130" customHeight="1">
-      <c r="A12" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B12" s="7" t="inlineStr">
+・最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="140" customHeight="1">
+      <c r="A13" s="6" t="n">
+        <v>8</v>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>お風呂</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>【毎回】
 ・浴槽：専用洗剤を吹きかけ、30秒後に流す
 ・床、壁（手の届く低い所）を洗う
 ・椅子、シャンプーを置いているテーブルを洗う（ボトルの底のぬめりも）
 ・排水口の髪の毛を取って捨てる
+・扉のホコリを取る（通気口・枠など）
 【月1回】壁全体（手の届く範囲）、ドア、ゴムパッキンまでしっかり洗う
-【2か月に1回】掃除が終わったら防カビくん煙剤をたく（手順の注意を参照）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="42" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>床</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>・毎回：掃除機をかける
-・2週に1回（対象の週）：掃除機のあと、クイックルワイパー（ウエット）で拭く</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="52" customHeight="1">
+【2か月に1回】掃除が終わったら防カビくん煙剤をたく（下の注意を参照）</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="66" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
       <c r="B14" s="7" t="inlineStr">
         <is>
-          <t>靴磨き・消臭</t>
+          <t>玄関・消臭</t>
         </is>
       </c>
       <c r="C14" s="8" t="inlineStr">
         <is>
-          <t>・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
-・毎回：玄関の靴、カーテン、ソファなどの布製品に消臭スプレーをかける
+          <t>・出ている靴はすべて靴箱にしまう
+・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
+・毎回：靴、カーテン、ソファなどの布製品に消臭スプレーをかける
 　（革製品・シルクなど、スプレーの表示で使えない素材にはかけない）</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="52" customHeight="1">
+    <row r="15" ht="48" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>10</v>
       </c>
       <c r="B15" s="7" t="inlineStr">
         <is>
+          <t>床・玄関</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>・毎回：部屋の床と玄関に掃除機をかける
+・2週に1回（対象の週）：掃除機のあと、床をクイックルワイパー（ウエット）で拭く</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="52" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
           <t>洗濯物を干す</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>・横のカゴに入れてベランダへ持っていき、干す
 ・風が強い日は、竿の下のフックにかける
@@ -787,48 +822,52 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="34" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>洗濯機の後始末</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="34" customHeight="1">
+    <row r="17" ht="22" customHeight="1">
       <c r="A17" s="6" t="n">
         <v>12</v>
       </c>
       <c r="B17" s="7" t="inlineStr">
         <is>
-          <t>燃えるゴミ</t>
+          <t>洗濯機の後始末</t>
         </is>
       </c>
       <c r="C17" s="8" t="inlineStr">
         <is>
-          <t>・家中のゴミをまとめて出す（量が少なくても毎回。収集は14時ごろ）</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="8" customHeight="1"/>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="4" t="inlineStr">
+          <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="118" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>ゴミ（最後に）</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>・家中のゴミ箱を集め、中身を1つの袋にまとめて燃えるゴミとして出す（量が少なくても毎回。収集は14時ごろ）
+・ゴミ箱に袋が付いていても、袋は替えずに中身だけ移す（洗面台の鏡の中のゴミ箱の袋は月1回交換）
+・袋が付いていないゴミ箱には、新しい袋を付ける
+・ゴミ箱の中が汚れていたら掃除する
+・燃えるゴミ以外（缶・びん・ペットボトルなど）が混ざっていたら、よけておく</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="8" customHeight="1"/>
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="4" t="inlineStr">
         <is>
           <t>お風呂の防カビくん煙剤（2か月に1回）</t>
         </is>
       </c>
-      <c r="B19" s="5" t="n"/>
-      <c r="C19" s="5" t="n"/>
-    </row>
-    <row r="20" ht="66" customHeight="1">
-      <c r="A20" s="3" t="inlineStr">
+      <c r="B20" s="5" t="n"/>
+      <c r="C20" s="5" t="n"/>
+    </row>
+    <row r="21" ht="66" customHeight="1">
+      <c r="A21" s="3" t="inlineStr">
         <is>
           <t>・お風呂掃除が終わってからたく。シャンプー等の置き方、濡れたままでよいか、待ち時間は、製品の説明書きに従ってください
 ・たいている間は浴室のドア・窓を閉め、換気扇を止め、浴室に入らない
@@ -836,36 +875,36 @@
         </is>
       </c>
     </row>
-    <row r="21" ht="8" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
+    <row r="22" ht="8" customHeight="1"/>
+    <row r="23" ht="22" customHeight="1">
+      <c r="A23" s="4" t="inlineStr">
         <is>
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="56" customHeight="1">
-      <c r="A23" s="9" t="inlineStr">
+      <c r="B23" s="5" t="n"/>
+      <c r="C23" s="5" t="n"/>
+    </row>
+    <row r="24" ht="56" customHeight="1">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>・パイプユニッシュ（塩素系）は、酸性の洗剤やクエン酸と絶対に混ぜない。使っている間は換気する
 ・高い所の作業や、無理な姿勢での作業はしなくて構いません
 ・気づいたこと、足りない洗剤などは、チェックリストの連絡事項に書いてください</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
+      <c r="B24" s="5" t="n"/>
+      <c r="C24" s="5" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="8">
-    <mergeCell ref="A19:C19"/>
     <mergeCell ref="A1:C1"/>
     <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
-    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A20:C20"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -880,10 +919,10 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F35"/>
+  <dimension ref="A1:F36"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
-    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="47" customWidth="1" min="1" max="1"/>
     <col width="10" customWidth="1" min="2" max="2"/>
     <col width="10" customWidth="1" min="3" max="3"/>
     <col width="10" customWidth="1" min="4" max="4"/>
@@ -1017,7 +1056,7 @@
     <row r="10" ht="22" customHeight="1">
       <c r="A10" s="8" t="inlineStr">
         <is>
-          <t>ベッドメイキング</t>
+          <t>寝室（ベッドメイキング・フレーム・台のホコリ）</t>
         </is>
       </c>
       <c r="B10" s="14" t="n"/>
@@ -1029,7 +1068,7 @@
     <row r="11" ht="22" customHeight="1">
       <c r="A11" s="8" t="inlineStr">
         <is>
-          <t>トイレ</t>
+          <t>テーブル（食卓・仕事用ガラス）</t>
         </is>
       </c>
       <c r="B11" s="14" t="n"/>
@@ -1041,7 +1080,7 @@
     <row r="12" ht="22" customHeight="1">
       <c r="A12" s="8" t="inlineStr">
         <is>
-          <t>洗面台（ボウル・排水口・乾拭き）</t>
+          <t>トイレ</t>
         </is>
       </c>
       <c r="B12" s="14" t="n"/>
@@ -1053,7 +1092,7 @@
     <row r="13" ht="22" customHeight="1">
       <c r="A13" s="8" t="inlineStr">
         <is>
-          <t>洗面台の鏡の中のゴミ箱</t>
+          <t>洗面台（ボウル・排水口・乾拭き）</t>
         </is>
       </c>
       <c r="B13" s="14" t="n"/>
@@ -1065,7 +1104,7 @@
     <row r="14" ht="22" customHeight="1">
       <c r="A14" s="8" t="inlineStr">
         <is>
-          <t>お風呂（浴槽・床・壁・椅子・台・排水口）</t>
+          <t>お風呂（浴槽・床・壁・椅子・台・排水口・扉）</t>
         </is>
       </c>
       <c r="B14" s="14" t="n"/>
@@ -1077,7 +1116,7 @@
     <row r="15" ht="22" customHeight="1">
       <c r="A15" s="8" t="inlineStr">
         <is>
-          <t>床の掃除機がけ</t>
+          <t>玄関の靴をしまう</t>
         </is>
       </c>
       <c r="B15" s="14" t="n"/>
@@ -1089,7 +1128,7 @@
     <row r="16" ht="22" customHeight="1">
       <c r="A16" s="8" t="inlineStr">
         <is>
-          <t>消臭スプレー（靴・カーテン・ソファ等）</t>
+          <t>床・玄関の掃除機がけ</t>
         </is>
       </c>
       <c r="B16" s="14" t="n"/>
@@ -1101,7 +1140,7 @@
     <row r="17" ht="22" customHeight="1">
       <c r="A17" s="8" t="inlineStr">
         <is>
-          <t>洗濯物を干す</t>
+          <t>消臭スプレー（靴・カーテン・ソファ等）</t>
         </is>
       </c>
       <c r="B17" s="14" t="n"/>
@@ -1113,7 +1152,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>洗濯機のフタを開けて乾かす</t>
+          <t>洗濯物を干す</t>
         </is>
       </c>
       <c r="B18" s="14" t="n"/>
@@ -1125,7 +1164,7 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>燃えるゴミ出し</t>
+          <t>洗濯機のフタを開けて乾かす</t>
         </is>
       </c>
       <c r="B19" s="14" t="n"/>
@@ -1134,60 +1173,48 @@
       <c r="E19" s="14" t="n"/>
       <c r="F19" s="14" t="n"/>
     </row>
-    <row r="20" ht="18" customHeight="1">
-      <c r="A20" s="13" t="inlineStr">
+    <row r="20" ht="22" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>ゴミ箱を集めて燃えるゴミ出し</t>
+        </is>
+      </c>
+      <c r="B20" s="14" t="n"/>
+      <c r="C20" s="14" t="n"/>
+      <c r="D20" s="14" t="n"/>
+      <c r="E20" s="14" t="n"/>
+      <c r="F20" s="14" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="13" t="inlineStr">
         <is>
           <t>【2週に1回】</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-      <c r="D20" s="5" t="n"/>
-      <c r="E20" s="5" t="n"/>
-      <c r="F20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>パイプユニッシュ（キッチン・お風呂）</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F21" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B21" s="5" t="n"/>
+      <c r="C21" s="5" t="n"/>
+      <c r="D21" s="5" t="n"/>
+      <c r="E21" s="5" t="n"/>
+      <c r="F21" s="5" t="n"/>
     </row>
     <row r="22" ht="22" customHeight="1">
       <c r="A22" s="8" t="inlineStr">
         <is>
-          <t>シーツ・枕カバーの洗濯</t>
-        </is>
-      </c>
-      <c r="B22" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C22" s="14" t="n"/>
-      <c r="D22" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E22" s="14" t="n"/>
+          <t>パイプユニッシュ（キッチン・お風呂）</t>
+        </is>
+      </c>
+      <c r="B22" s="14" t="n"/>
+      <c r="C22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D22" s="14" t="n"/>
+      <c r="E22" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F22" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1197,7 +1224,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>床のクイックルワイパー（ウエット）</t>
+          <t>シーツ・枕カバーの洗濯</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
@@ -1218,58 +1245,54 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="18" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>床のクイックルワイパー（ウエット）</t>
+        </is>
+      </c>
+      <c r="B24" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="14" t="n"/>
+      <c r="D24" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="14" t="n"/>
+      <c r="F24" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="13" t="inlineStr">
         <is>
           <t>【月1回】</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
-      <c r="D24" s="5" t="n"/>
-      <c r="E24" s="5" t="n"/>
-      <c r="F24" s="5" t="n"/>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>靴磨き（靴クリーム）</t>
-        </is>
-      </c>
-      <c r="B25" s="14" t="n"/>
-      <c r="C25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+      <c r="D25" s="5" t="n"/>
+      <c r="E25" s="5" t="n"/>
+      <c r="F25" s="5" t="n"/>
     </row>
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>パイプユニッシュ（洗面台）</t>
-        </is>
-      </c>
-      <c r="B26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C26" s="14" t="n"/>
+          <t>靴磨き（靴クリーム）</t>
+        </is>
+      </c>
+      <c r="B26" s="14" t="n"/>
+      <c r="C26" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D26" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1289,7 +1312,7 @@
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>撥水コート（シンク・洗面台）</t>
+          <t>パイプユニッシュ（洗面台）</t>
         </is>
       </c>
       <c r="B27" s="15" t="inlineStr">
@@ -1297,12 +1320,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="14" t="n"/>
+      <c r="C27" s="14" t="n"/>
+      <c r="D27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E27" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1317,7 +1340,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
+          <t>撥水コート（シンク・洗面台）</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -1330,12 +1353,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="14" t="n"/>
+      <c r="D28" s="14" t="n"/>
+      <c r="E28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F28" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1345,7 +1368,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>洗面台ゴミ箱の袋交換</t>
+          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
@@ -1370,62 +1393,78 @@
         </is>
       </c>
     </row>
-    <row r="30" ht="18" customHeight="1">
-      <c r="A30" s="13" t="inlineStr">
+    <row r="30" ht="22" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>洗面台ゴミ箱の袋交換</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C30" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="14" t="n"/>
+      <c r="F30" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="31" ht="18" customHeight="1">
+      <c r="A31" s="13" t="inlineStr">
         <is>
           <t>【2か月に1回（　　月・　　月・　　月…）】</t>
         </is>
       </c>
-      <c r="B30" s="5" t="n"/>
-      <c r="C30" s="5" t="n"/>
-      <c r="D30" s="5" t="n"/>
-      <c r="E30" s="5" t="n"/>
-      <c r="F30" s="5" t="n"/>
-    </row>
-    <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="B31" s="5" t="n"/>
+      <c r="C31" s="5" t="n"/>
+      <c r="D31" s="5" t="n"/>
+      <c r="E31" s="5" t="n"/>
+      <c r="F31" s="5" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
         <is>
           <t>お風呂の防カビくん煙剤（対象月のみ）</t>
         </is>
       </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="30" customHeight="1">
-      <c r="A32" s="16" t="inlineStr">
+      <c r="B32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E32" s="14" t="n"/>
+      <c r="F32" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="33" ht="30" customHeight="1">
+      <c r="A33" s="16" t="inlineStr">
         <is>
           <t>作業時間（開始〜終了）</t>
-        </is>
-      </c>
-      <c r="B32" s="5" t="n"/>
-      <c r="C32" s="5" t="n"/>
-      <c r="D32" s="5" t="n"/>
-      <c r="E32" s="5" t="n"/>
-      <c r="F32" s="5" t="n"/>
-    </row>
-    <row r="33" ht="26" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>作業員サイン</t>
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
@@ -1434,10 +1473,10 @@
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
     </row>
-    <row r="34" ht="70" customHeight="1">
+    <row r="34" ht="26" customHeight="1">
       <c r="A34" s="16" t="inlineStr">
         <is>
-          <t>連絡事項</t>
+          <t>作業員サイン</t>
         </is>
       </c>
       <c r="B34" s="5" t="n"/>
@@ -1446,8 +1485,20 @@
       <c r="E34" s="5" t="n"/>
       <c r="F34" s="5" t="n"/>
     </row>
-    <row r="35">
-      <c r="A35" s="11" t="inlineStr">
+    <row r="35" ht="70" customHeight="1">
+      <c r="A35" s="16" t="inlineStr">
+        <is>
+          <t>連絡事項</t>
+        </is>
+      </c>
+      <c r="B35" s="5" t="n"/>
+      <c r="C35" s="5" t="n"/>
+      <c r="D35" s="5" t="n"/>
+      <c r="E35" s="5" t="n"/>
+      <c r="F35" s="5" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
         <is>
           <t>※第5月曜がない月は、第5月曜の欄は使いません。作業の詳しい手順は「作業手順書」を見てください。</t>
         </is>
@@ -1455,13 +1506,805 @@
     </row>
   </sheetData>
   <mergeCells count="7">
-    <mergeCell ref="A24:F24"/>
     <mergeCell ref="A2:F2"/>
+    <mergeCell ref="A36:F36"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="A31:F31"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A20:F20"/>
-    <mergeCell ref="A30:F30"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A25:F25"/>
+  </mergeCells>
+  <printOptions horizontalCentered="1"/>
+  <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:E36"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="34" customWidth="1" min="2" max="2"/>
+    <col width="34" customWidth="1" min="3" max="3"/>
+    <col width="12" customWidth="1" min="4" max="4"/>
+    <col width="8" customWidth="1" min="5" max="5"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="28" customHeight="1">
+      <c r="A1" s="10" t="inlineStr">
+        <is>
+          <t>家事代行　道具・洗剤リスト</t>
+        </is>
+      </c>
+    </row>
+    <row r="2" ht="26" customHeight="1">
+      <c r="A2" s="17" t="inlineStr">
+        <is>
+          <t>「在庫」欄に、ある物は○、買う物は×をつけてください。「必要度」が「あると便利」の物は、なくても作業できます。</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" ht="22" customHeight="1">
+      <c r="A3" s="18" t="inlineStr">
+        <is>
+          <t>場所</t>
+        </is>
+      </c>
+      <c r="B3" s="18" t="inlineStr">
+        <is>
+          <t>アイテム</t>
+        </is>
+      </c>
+      <c r="C3" s="18" t="inlineStr">
+        <is>
+          <t>使う作業・メモ</t>
+        </is>
+      </c>
+      <c r="D3" s="18" t="inlineStr">
+        <is>
+          <t>必要度</t>
+        </is>
+      </c>
+      <c r="E3" s="18" t="inlineStr">
+        <is>
+          <t>在庫</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="8" t="inlineStr">
+        <is>
+          <t>洗濯</t>
+        </is>
+      </c>
+      <c r="B4" s="7" t="inlineStr">
+        <is>
+          <t>洗濯用洗剤</t>
+        </is>
+      </c>
+      <c r="C4" s="19" t="inlineStr"/>
+      <c r="D4" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E4" s="20" t="n"/>
+    </row>
+    <row r="5" ht="20" customHeight="1">
+      <c r="A5" s="8" t="inlineStr">
+        <is>
+          <t>洗濯</t>
+        </is>
+      </c>
+      <c r="B5" s="7" t="inlineStr">
+        <is>
+          <t>洗濯ネット</t>
+        </is>
+      </c>
+      <c r="C5" s="19" t="inlineStr">
+        <is>
+          <t>ボクサーパンツなど傷みやすい物</t>
+        </is>
+      </c>
+      <c r="D5" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E5" s="20" t="n"/>
+    </row>
+    <row r="6" ht="30" customHeight="1">
+      <c r="A6" s="8" t="inlineStr">
+        <is>
+          <t>洗濯</t>
+        </is>
+      </c>
+      <c r="B6" s="7" t="inlineStr">
+        <is>
+          <t>ピンチハンガー・ハンガー・洗濯ばさみ</t>
+        </is>
+      </c>
+      <c r="C6" s="19" t="inlineStr">
+        <is>
+          <t>干す用</t>
+        </is>
+      </c>
+      <c r="D6" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E6" s="20" t="n"/>
+    </row>
+    <row r="7" ht="20" customHeight="1">
+      <c r="A7" s="8" t="inlineStr">
+        <is>
+          <t>洗濯</t>
+        </is>
+      </c>
+      <c r="B7" s="7" t="inlineStr">
+        <is>
+          <t>古歯ブラシ</t>
+        </is>
+      </c>
+      <c r="C7" s="19" t="inlineStr">
+        <is>
+          <t>洗濯機フィルターのゴミ取り</t>
+        </is>
+      </c>
+      <c r="D7" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E7" s="20" t="n"/>
+    </row>
+    <row r="8" ht="20" customHeight="1">
+      <c r="A8" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B8" s="7" t="inlineStr">
+        <is>
+          <t>食器用洗剤</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr"/>
+      <c r="D8" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E8" s="20" t="n"/>
+    </row>
+    <row r="9" ht="20" customHeight="1">
+      <c r="A9" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B9" s="7" t="inlineStr">
+        <is>
+          <t>食器用スポンジ</t>
+        </is>
+      </c>
+      <c r="C9" s="19" t="inlineStr"/>
+      <c r="D9" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E9" s="20" t="n"/>
+    </row>
+    <row r="10" ht="20" customHeight="1">
+      <c r="A10" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B10" s="7" t="inlineStr">
+        <is>
+          <t>ボトルブラシ</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr">
+        <is>
+          <t>プロテインシェイカーのこびり付き</t>
+        </is>
+      </c>
+      <c r="D10" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E10" s="20" t="n"/>
+    </row>
+    <row r="11" ht="20" customHeight="1">
+      <c r="A11" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="inlineStr">
+        <is>
+          <t>食洗機用洗剤</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr"/>
+      <c r="D11" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E11" s="20" t="n"/>
+    </row>
+    <row r="12" ht="20" customHeight="1">
+      <c r="A12" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="inlineStr">
+        <is>
+          <t>コンロ用洗剤（油汚れ用）</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr">
+        <is>
+          <t>ガスコンロ・天板</t>
+        </is>
+      </c>
+      <c r="D12" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E12" s="20" t="n"/>
+    </row>
+    <row r="13" ht="20" customHeight="1">
+      <c r="A13" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="inlineStr">
+        <is>
+          <t>排水口ネット</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>排水口のゴミ受け</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="30" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>シンク・洗面台用 撥水コート剤</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>月1回。水回り兼用の物なら1本で両方に使えます</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="30" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>排水口</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>パイプユニッシュ</t>
+        </is>
+      </c>
+      <c r="C15" s="19" t="inlineStr">
+        <is>
+          <t>キッチン・お風呂は2週に1回、洗面台は月1回</t>
+        </is>
+      </c>
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="n"/>
+    </row>
+    <row r="16" ht="20" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
+        <is>
+          <t>トイレ用洗剤・トイレブラシ</t>
+        </is>
+      </c>
+      <c r="C16" s="19" t="inlineStr">
+        <is>
+          <t>上の棚</t>
+        </is>
+      </c>
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
+        <is>
+          <t>トイレ</t>
+        </is>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
+        <is>
+          <t>トイレ掃除用シート</t>
+        </is>
+      </c>
+      <c r="C17" s="19" t="inlineStr">
+        <is>
+          <t>便座・床の拭き掃除</t>
+        </is>
+      </c>
+      <c r="D17" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E17" s="20" t="n"/>
+    </row>
+    <row r="18" ht="20" customHeight="1">
+      <c r="A18" s="8" t="inlineStr">
+        <is>
+          <t>洗面台</t>
+        </is>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>スポンジ（洗面台用）</t>
+        </is>
+      </c>
+      <c r="C18" s="19" t="inlineStr">
+        <is>
+          <t>ボウルをこする</t>
+        </is>
+      </c>
+      <c r="D18" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E18" s="20" t="n"/>
+    </row>
+    <row r="19" ht="20" customHeight="1">
+      <c r="A19" s="8" t="inlineStr">
+        <is>
+          <t>洗面台・お風呂</t>
+        </is>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
+        <is>
+          <t>排水口用の小さいブラシ</t>
+        </is>
+      </c>
+      <c r="C19" s="19" t="inlineStr">
+        <is>
+          <t>髪の毛・ぬめり取り</t>
+        </is>
+      </c>
+      <c r="D19" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E19" s="20" t="n"/>
+    </row>
+    <row r="20" ht="30" customHeight="1">
+      <c r="A20" s="8" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
+        <is>
+          <t>浴槽用スプレー洗剤（30秒で流すタイプ）</t>
+        </is>
+      </c>
+      <c r="C20" s="19" t="inlineStr">
+        <is>
+          <t>使用中の物</t>
+        </is>
+      </c>
+      <c r="D20" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E20" s="20" t="n"/>
+    </row>
+    <row r="21" ht="20" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>浴室用スポンジ・柄つきブラシ</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>床・壁・椅子・テーブル</t>
+        </is>
+      </c>
+      <c r="D21" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="n"/>
+    </row>
+    <row r="22" ht="20" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="B22" s="7" t="inlineStr">
+        <is>
+          <t>防カビくん煙剤</t>
+        </is>
+      </c>
+      <c r="C22" s="19" t="inlineStr">
+        <is>
+          <t>2か月に1回（年6個）</t>
+        </is>
+      </c>
+      <c r="D22" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E22" s="20" t="n"/>
+    </row>
+    <row r="23" ht="20" customHeight="1">
+      <c r="A23" s="8" t="inlineStr">
+        <is>
+          <t>ホコリ取り</t>
+        </is>
+      </c>
+      <c r="B23" s="7" t="inlineStr">
+        <is>
+          <t>ハンディモップ（替えシートも）</t>
+        </is>
+      </c>
+      <c r="C23" s="19" t="inlineStr">
+        <is>
+          <t>テーブル・ベッドフレーム・台・お風呂の扉</t>
+        </is>
+      </c>
+      <c r="D23" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E23" s="20" t="n"/>
+    </row>
+    <row r="24" ht="30" customHeight="1">
+      <c r="A24" s="8" t="inlineStr">
+        <is>
+          <t>拭き掃除</t>
+        </is>
+      </c>
+      <c r="B24" s="7" t="inlineStr">
+        <is>
+          <t>マイクロファイバークロス（数枚）</t>
+        </is>
+      </c>
+      <c r="C24" s="19" t="inlineStr">
+        <is>
+          <t>水拭き用・乾拭き用に分ける。ガラスのテーブル・シンク・洗面台</t>
+        </is>
+      </c>
+      <c r="D24" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E24" s="20" t="n"/>
+    </row>
+    <row r="25" ht="20" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>拭き掃除</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>ガラス用クリーナー</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>ガラスのテーブルの汚れがひどい時</t>
+        </is>
+      </c>
+      <c r="D25" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="n"/>
+    </row>
+    <row r="26" ht="20" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>掃除機</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>部屋と玄関</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="30" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
+        <is>
+          <t>クイックルワイパー（ウエットシート）</t>
+        </is>
+      </c>
+      <c r="C27" s="19" t="inlineStr">
+        <is>
+          <t>2週に1回</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E27" s="20" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
+        <is>
+          <t>玄関</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>靴クリーム（靴の色に合わせる）</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>月1回の靴磨き</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
+          <t>玄関</t>
+        </is>
+      </c>
+      <c r="B29" s="7" t="inlineStr">
+        <is>
+          <t>靴磨き用ブラシ・布</t>
+        </is>
+      </c>
+      <c r="C29" s="19" t="inlineStr"/>
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="n"/>
+    </row>
+    <row r="30" ht="20" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
+        <is>
+          <t>消臭</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>布用消臭スプレー</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>靴・カーテン・ソファ。毎回</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="n"/>
+    </row>
+    <row r="31" ht="20" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>ゴミ</t>
+        </is>
+      </c>
+      <c r="B31" s="7" t="inlineStr">
+        <is>
+          <t>名古屋市指定ごみ袋（可燃用）</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr">
+        <is>
+          <t>燃えるゴミを出す袋</t>
+        </is>
+      </c>
+      <c r="D31" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E31" s="20" t="n"/>
+    </row>
+    <row r="32" ht="20" customHeight="1">
+      <c r="A32" s="8" t="inlineStr">
+        <is>
+          <t>ゴミ</t>
+        </is>
+      </c>
+      <c r="B32" s="7" t="inlineStr">
+        <is>
+          <t>ゴミ箱用の袋</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr">
+        <is>
+          <t>袋が付いていないゴミ箱に付ける</t>
+        </is>
+      </c>
+      <c r="D32" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E32" s="20" t="n"/>
+    </row>
+    <row r="33" ht="20" customHeight="1">
+      <c r="A33" s="8" t="inlineStr">
+        <is>
+          <t>ゴミ</t>
+        </is>
+      </c>
+      <c r="B33" s="7" t="inlineStr">
+        <is>
+          <t>除菌シート</t>
+        </is>
+      </c>
+      <c r="C33" s="19" t="inlineStr">
+        <is>
+          <t>汚れたゴミ箱の中の掃除</t>
+        </is>
+      </c>
+      <c r="D33" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E33" s="20" t="n"/>
+    </row>
+    <row r="34" ht="20" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>寝室</t>
+        </is>
+      </c>
+      <c r="B34" s="7" t="inlineStr">
+        <is>
+          <t>替えのシーツ・枕カバー（もう1組）</t>
+        </is>
+      </c>
+      <c r="C34" s="19" t="inlineStr">
+        <is>
+          <t>洗濯した物が乾かない日もすぐ交換できる</t>
+        </is>
+      </c>
+      <c r="D34" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E34" s="20" t="n"/>
+    </row>
+    <row r="35" ht="20" customHeight="1">
+      <c r="A35" s="8" t="inlineStr">
+        <is>
+          <t>共通</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>ゴム手袋・使い捨て手袋</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>トイレ・お風呂・排水口・ゴミ箱</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="n"/>
+    </row>
+    <row r="36">
+      <c r="A36" s="11" t="inlineStr">
+        <is>
+          <t>※パイプユニッシュ（塩素系）と酸性の洗剤（クエン酸など）は、同じ場所に置かず、混ぜないでください。</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="3">
+    <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A36:E36"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -685,7 +685,7 @@
         </is>
       </c>
     </row>
-    <row r="9" ht="36" customHeight="1">
+    <row r="9" ht="46" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>4</v>
       </c>
@@ -696,7 +696,7 @@
       </c>
       <c r="C9" s="8" t="inlineStr">
         <is>
-          <t>・ベッドメイキング（シーツ類を洗う週は、洗ったものに交換する）
+          <t>・ベッドメイキング（シーツ類を洗う週は、予備のシーツ・枕カバーに交換し、外した物を洗濯する）
 ・ベッドフレーム、ティッシュを置いている台のホコリを取る</t>
         </is>
       </c>
@@ -771,7 +771,7 @@
         </is>
       </c>
     </row>
-    <row r="14" ht="66" customHeight="1">
+    <row r="14" ht="80" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
@@ -784,6 +784,7 @@
         <is>
           <t>・出ている靴はすべて靴箱にしまう
 ・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
+　黒い靴は黒用、白い靴は白用のクリームを使い分ける（黒・白以外の色の靴は磨かずに残す）
 ・毎回：靴、カーテン、ソファなどの布製品に消臭スプレーをかける
 　（革製品・シルクなど、スプレーの表示で使えない素材にはかけない）</t>
         </is>
@@ -1224,7 +1225,7 @@
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>シーツ・枕カバーの洗濯</t>
+          <t>シーツ・枕カバーを予備に交換して洗濯</t>
         </is>
       </c>
       <c r="B23" s="15" t="inlineStr">
@@ -1284,7 +1285,7 @@
     <row r="26" ht="22" customHeight="1">
       <c r="A26" s="8" t="inlineStr">
         <is>
-          <t>靴磨き（靴クリーム）</t>
+          <t>靴磨き（黒用・白用クリームを使い分け）</t>
         </is>
       </c>
       <c r="B26" s="14" t="n"/>
@@ -2113,7 +2114,7 @@
       </c>
       <c r="E27" s="20" t="n"/>
     </row>
-    <row r="28" ht="20" customHeight="1">
+    <row r="28" ht="30" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
           <t>玄関</t>
@@ -2121,12 +2122,12 @@
       </c>
       <c r="B28" s="7" t="inlineStr">
         <is>
-          <t>靴クリーム（靴の色に合わせる）</t>
+          <t>靴クリーム（黒用・白用）</t>
         </is>
       </c>
       <c r="C28" s="19" t="inlineStr">
         <is>
-          <t>月1回の靴磨き</t>
+          <t>月1回の靴磨き。靴の色に合わせて使い分ける</t>
         </is>
       </c>
       <c r="D28" s="20" t="inlineStr">
@@ -2255,17 +2256,17 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>替えのシーツ・枕カバー（もう1組）</t>
+          <t>予備のシーツ・枕カバー</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>洗濯した物が乾かない日もすぐ交換できる</t>
-        </is>
-      </c>
-      <c r="D34" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+          <t>シーツ類を洗う週に交換する（予備あり）</t>
+        </is>
+      </c>
+      <c r="D34" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E34" s="20" t="n"/>

--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -14,7 +14,7 @@
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$24</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'道具・洗剤リスト'!$A$1:$E$36</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'道具・洗剤リスト'!$A$1:$E$38</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -628,7 +628,7 @@
       <c r="B5" s="5" t="n"/>
       <c r="C5" s="5" t="n"/>
     </row>
-    <row r="6" ht="92" customHeight="1">
+    <row r="6" ht="108" customHeight="1">
       <c r="A6" s="6" t="n">
         <v>1</v>
       </c>
@@ -644,11 +644,12 @@
 ・洗濯機を回す
 ・乾燥機にかけるもの：タオル、靴下など
 ・乾燥機にかけないもの：ボクサーパンツ（必ず干す）、その他の衣類
-※洗濯機のフタが壊れています。開け閉めはゆっくり注意して行ってください</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="62" customHeight="1">
+※洗濯機のフタが壊れています。開け閉めはゆっくり注意して行ってください
+【使う道具】洗濯用洗剤、洗濯ネット、古歯ブラシ（フィルター）</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="78" customHeight="1">
       <c r="A7" s="6" t="n">
         <v>2</v>
       </c>
@@ -662,11 +663,12 @@
         <is>
           <t>・チェックリストで対象になっている週は、この時点で浴室・洗面台の排水口に入れる
 ・15〜30分たったら、たっぷりの水で流す（長時間放置しない）
-・キッチンは、洗い物が終わってから入れる（手順3）</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="106" customHeight="1">
+・キッチンは、洗い物が終わってから入れる（手順3）
+【使う道具】パイプユニッシュ、ゴム手袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="146" customHeight="1">
       <c r="A8" s="6" t="n">
         <v>3</v>
       </c>
@@ -681,11 +683,12 @@
 ・プロテインシェイカーは、こびり付いていることがあるので、スポンジでこすって泡を流してから食洗機へ
 ・ガスコンロと天板を掃除する
 ・排水口のゴミを取って捨てる（対象の週はここでパイプユニッシュを入れる）
-・シンクは最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="46" customHeight="1">
+・シンクは最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
+【使う道具】食器用洗剤・スポンジ、ボトルブラシ、食洗機用洗剤、コンロ用洗剤、シンク用スポンジ、排水口ネット、クロス（乾拭き用）、撥水コート剤、ゴム手袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="62" customHeight="1">
       <c r="A9" s="6" t="n">
         <v>4</v>
       </c>
@@ -697,11 +700,12 @@
       <c r="C9" s="8" t="inlineStr">
         <is>
           <t>・ベッドメイキング（シーツ類を洗う週は、予備のシーツ・枕カバーに交換し、外した物を洗濯する）
-・ベッドフレーム、ティッシュを置いている台のホコリを取る</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="44" customHeight="1">
+・ベッドフレーム、ティッシュを置いている台のホコリを取る
+【使う道具】予備のシーツ・枕カバー、ハンディモップ</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="60" customHeight="1">
       <c r="A10" s="6" t="n">
         <v>5</v>
       </c>
@@ -713,11 +717,12 @@
       <c r="C10" s="8" t="inlineStr">
         <is>
           <t>・食卓のテーブル、仕事用のテーブル（ガラス）のホコリをハンディモップで取る
-・汚れている場合は、水拭き → 乾拭き</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1">
+・汚れている場合は、水拭き → 乾拭き
+【使う道具】ハンディモップ、クロス（水拭き用・乾拭き用）、ガラス用クリーナー（汚れがひどい時）</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="40" customHeight="1">
       <c r="A11" s="6" t="n">
         <v>6</v>
       </c>
@@ -728,11 +733,12 @@
       </c>
       <c r="C11" s="8" t="inlineStr">
         <is>
-          <t>・トイレ掃除（掃除道具は上の棚にあります）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="52" customHeight="1">
+          <t>・トイレ掃除（掃除道具は上の棚にあります）
+【使う道具】トイレ用洗剤、トイレブラシ、トイレ掃除用シート、使い捨て手袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="68" customHeight="1">
       <c r="A12" s="6" t="n">
         <v>7</v>
       </c>
@@ -745,11 +751,12 @@
         <is>
           <t>・ボウルをこすって掃除する
 ・排水口のゴミ・髪の毛を取って掃除する
-・最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="140" customHeight="1">
+・最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
+【使う道具】洗面台用スポンジ、排水口用ブラシ、クロス（乾拭き用）、撥水コート剤</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="174" customHeight="1">
       <c r="A13" s="6" t="n">
         <v>8</v>
       </c>
@@ -767,11 +774,12 @@
 ・排水口の髪の毛を取って捨てる
 ・扉のホコリを取る（通気口・枠など）
 【月1回】壁全体（手の届く範囲）、ドア、ゴムパッキンまでしっかり洗う
-【2か月に1回】掃除が終わったら防カビくん煙剤をたく（下の注意を参照）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="80" customHeight="1">
+【2か月に1回】掃除が終わったら防カビくん煙剤をたく（下の注意を参照）
+【使う道具】浴槽用スプレー洗剤、浴室用スポンジ・柄つきブラシ、排水口用ブラシ、ハンディモップ（扉）、防カビくん煙剤、ゴム手袋</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="112" customHeight="1">
       <c r="A14" s="6" t="n">
         <v>9</v>
       </c>
@@ -786,11 +794,12 @@
 ・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
 　黒い靴は黒用、白い靴は白用のクリームを使い分ける（黒・白以外の色の靴は磨かずに残す）
 ・毎回：靴、カーテン、ソファなどの布製品に消臭スプレーをかける
-　（革製品・シルクなど、スプレーの表示で使えない素材にはかけない）</t>
-        </is>
-      </c>
-    </row>
-    <row r="15" ht="48" customHeight="1">
+　（革製品・シルクなど、スプレーの表示で使えない素材にはかけない）
+【使う道具】靴クリーム（黒用・白用）、靴磨き用ブラシ・布、布用消臭スプレー</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="64" customHeight="1">
       <c r="A15" s="6" t="n">
         <v>10</v>
       </c>
@@ -802,11 +811,12 @@
       <c r="C15" s="8" t="inlineStr">
         <is>
           <t>・毎回：部屋の床と玄関に掃除機をかける
-・2週に1回（対象の週）：掃除機のあと、床をクイックルワイパー（ウエット）で拭く</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="52" customHeight="1">
+・2週に1回（対象の週）：掃除機のあと、床をクイックルワイパー（ウエット）で拭く
+【使う道具】掃除機、クイックルワイパー（ウエットシート）</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="68" customHeight="1">
       <c r="A16" s="6" t="n">
         <v>11</v>
       </c>
@@ -819,7 +829,8 @@
         <is>
           <t>・横のカゴに入れてベランダへ持っていき、干す
 ・風が強い日は、竿の下のフックにかける
-・乾燥機が終わっていれば、カゴに取り出しておく</t>
+・乾燥機が終わっていれば、カゴに取り出しておく
+【使う道具】洗濯カゴ、ピンチハンガー・ハンガー・洗濯ばさみ</t>
         </is>
       </c>
     </row>
@@ -838,7 +849,7 @@
         </is>
       </c>
     </row>
-    <row r="18" ht="118" customHeight="1">
+    <row r="18" ht="150" customHeight="1">
       <c r="A18" s="6" t="n">
         <v>13</v>
       </c>
@@ -853,7 +864,8 @@
 ・ゴミ箱に袋が付いていても、袋は替えずに中身だけ移す（洗面台の鏡の中のゴミ箱の袋は月1回交換）
 ・袋が付いていないゴミ箱には、新しい袋を付ける
 ・ゴミ箱の中が汚れていたら掃除する
-・燃えるゴミ以外（缶・びん・ペットボトルなど）が混ざっていたら、よけておく</t>
+・燃えるゴミ以外（缶・びん・ペットボトルなど）が混ざっていたら、よけておく
+【使う道具】名古屋市指定ごみ袋（可燃用）、ゴミ箱用の袋、除菌シート、使い捨て手袋</t>
         </is>
       </c>
     </row>
@@ -910,7 +922,7 @@
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -1527,7 +1539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E36"/>
+  <dimension ref="A1:E38"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1651,17 +1663,17 @@
       </c>
       <c r="B7" s="7" t="inlineStr">
         <is>
-          <t>古歯ブラシ</t>
+          <t>洗濯カゴ</t>
         </is>
       </c>
       <c r="C7" s="19" t="inlineStr">
         <is>
-          <t>洗濯機フィルターのゴミ取り</t>
-        </is>
-      </c>
-      <c r="D7" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+          <t>洗濯機の横にあり。ベランダに運ぶ</t>
+        </is>
+      </c>
+      <c r="D7" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E7" s="20" t="n"/>
@@ -1669,18 +1681,22 @@
     <row r="8" ht="20" customHeight="1">
       <c r="A8" s="8" t="inlineStr">
         <is>
-          <t>キッチン</t>
+          <t>洗濯</t>
         </is>
       </c>
       <c r="B8" s="7" t="inlineStr">
         <is>
-          <t>食器用洗剤</t>
-        </is>
-      </c>
-      <c r="C8" s="19" t="inlineStr"/>
-      <c r="D8" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
+          <t>古歯ブラシ</t>
+        </is>
+      </c>
+      <c r="C8" s="19" t="inlineStr">
+        <is>
+          <t>洗濯機フィルターのゴミ取り</t>
+        </is>
+      </c>
+      <c r="D8" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
         </is>
       </c>
       <c r="E8" s="20" t="n"/>
@@ -1693,7 +1709,7 @@
       </c>
       <c r="B9" s="7" t="inlineStr">
         <is>
-          <t>食器用スポンジ</t>
+          <t>食器用洗剤</t>
         </is>
       </c>
       <c r="C9" s="19" t="inlineStr"/>
@@ -1712,17 +1728,13 @@
       </c>
       <c r="B10" s="7" t="inlineStr">
         <is>
-          <t>ボトルブラシ</t>
-        </is>
-      </c>
-      <c r="C10" s="19" t="inlineStr">
-        <is>
-          <t>プロテインシェイカーのこびり付き</t>
-        </is>
-      </c>
-      <c r="D10" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+          <t>食器用スポンジ</t>
+        </is>
+      </c>
+      <c r="C10" s="19" t="inlineStr"/>
+      <c r="D10" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E10" s="20" t="n"/>
@@ -1735,13 +1747,17 @@
       </c>
       <c r="B11" s="7" t="inlineStr">
         <is>
-          <t>食洗機用洗剤</t>
-        </is>
-      </c>
-      <c r="C11" s="19" t="inlineStr"/>
-      <c r="D11" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
+          <t>ボトルブラシ</t>
+        </is>
+      </c>
+      <c r="C11" s="19" t="inlineStr">
+        <is>
+          <t>プロテインシェイカーのこびり付き</t>
+        </is>
+      </c>
+      <c r="D11" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
         </is>
       </c>
       <c r="E11" s="20" t="n"/>
@@ -1754,14 +1770,10 @@
       </c>
       <c r="B12" s="7" t="inlineStr">
         <is>
-          <t>コンロ用洗剤（油汚れ用）</t>
-        </is>
-      </c>
-      <c r="C12" s="19" t="inlineStr">
-        <is>
-          <t>ガスコンロ・天板</t>
-        </is>
-      </c>
+          <t>食洗機用洗剤</t>
+        </is>
+      </c>
+      <c r="C12" s="19" t="inlineStr"/>
       <c r="D12" s="20" t="inlineStr">
         <is>
           <t>必須</t>
@@ -1777,109 +1789,109 @@
       </c>
       <c r="B13" s="7" t="inlineStr">
         <is>
+          <t>コンロ用洗剤（油汚れ用）</t>
+        </is>
+      </c>
+      <c r="C13" s="19" t="inlineStr">
+        <is>
+          <t>ガスコンロ・天板</t>
+        </is>
+      </c>
+      <c r="D13" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E13" s="20" t="n"/>
+    </row>
+    <row r="14" ht="20" customHeight="1">
+      <c r="A14" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B14" s="7" t="inlineStr">
+        <is>
+          <t>シンク用スポンジ</t>
+        </is>
+      </c>
+      <c r="C14" s="19" t="inlineStr">
+        <is>
+          <t>シンクをこする（食器用とは別にする）</t>
+        </is>
+      </c>
+      <c r="D14" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E14" s="20" t="n"/>
+    </row>
+    <row r="15" ht="20" customHeight="1">
+      <c r="A15" s="8" t="inlineStr">
+        <is>
+          <t>キッチン</t>
+        </is>
+      </c>
+      <c r="B15" s="7" t="inlineStr">
+        <is>
           <t>排水口ネット</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C15" s="19" t="inlineStr">
         <is>
           <t>排水口のゴミ受け</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n"/>
-    </row>
-    <row r="14" ht="30" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="D15" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E15" s="20" t="n"/>
+    </row>
+    <row r="16" ht="30" customHeight="1">
+      <c r="A16" s="8" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>シンク・洗面台用 撥水コート剤</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C16" s="19" t="inlineStr">
         <is>
           <t>月1回。水回り兼用の物なら1本で両方に使えます</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n"/>
-    </row>
-    <row r="15" ht="30" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="D16" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E16" s="20" t="n"/>
+    </row>
+    <row r="17" ht="30" customHeight="1">
+      <c r="A17" s="8" t="inlineStr">
         <is>
           <t>排水口</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>パイプユニッシュ</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C17" s="19" t="inlineStr">
         <is>
           <t>キッチン・お風呂は2週に1回、洗面台は月1回</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="n"/>
-    </row>
-    <row r="16" ht="20" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>トイレ</t>
-        </is>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>トイレ用洗剤・トイレブラシ</t>
-        </is>
-      </c>
-      <c r="C16" s="19" t="inlineStr">
-        <is>
-          <t>上の棚</t>
-        </is>
-      </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n"/>
-    </row>
-    <row r="17" ht="20" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>トイレ</t>
-        </is>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>トイレ掃除用シート</t>
-        </is>
-      </c>
-      <c r="C17" s="19" t="inlineStr">
-        <is>
-          <t>便座・床の拭き掃除</t>
-        </is>
-      </c>
-      <c r="D17" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+      <c r="D17" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E17" s="20" t="n"/>
@@ -1887,17 +1899,17 @@
     <row r="18" ht="20" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>洗面台</t>
+          <t>トイレ</t>
         </is>
       </c>
       <c r="B18" s="7" t="inlineStr">
         <is>
-          <t>スポンジ（洗面台用）</t>
+          <t>トイレ用洗剤・トイレブラシ</t>
         </is>
       </c>
       <c r="C18" s="19" t="inlineStr">
         <is>
-          <t>ボウルをこする</t>
+          <t>上の棚</t>
         </is>
       </c>
       <c r="D18" s="20" t="inlineStr">
@@ -1910,17 +1922,17 @@
     <row r="19" ht="20" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>洗面台・お風呂</t>
+          <t>トイレ</t>
         </is>
       </c>
       <c r="B19" s="7" t="inlineStr">
         <is>
-          <t>排水口用の小さいブラシ</t>
+          <t>トイレ掃除用シート</t>
         </is>
       </c>
       <c r="C19" s="19" t="inlineStr">
         <is>
-          <t>髪の毛・ぬめり取り</t>
+          <t>便座・床の拭き掃除</t>
         </is>
       </c>
       <c r="D19" s="21" t="inlineStr">
@@ -1930,20 +1942,20 @@
       </c>
       <c r="E19" s="20" t="n"/>
     </row>
-    <row r="20" ht="30" customHeight="1">
+    <row r="20" ht="20" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>お風呂</t>
+          <t>洗面台</t>
         </is>
       </c>
       <c r="B20" s="7" t="inlineStr">
         <is>
-          <t>浴槽用スプレー洗剤（30秒で流すタイプ）</t>
+          <t>スポンジ（洗面台用）</t>
         </is>
       </c>
       <c r="C20" s="19" t="inlineStr">
         <is>
-          <t>使用中の物</t>
+          <t>ボウルをこする</t>
         </is>
       </c>
       <c r="D20" s="20" t="inlineStr">
@@ -1956,40 +1968,40 @@
     <row r="21" ht="20" customHeight="1">
       <c r="A21" s="8" t="inlineStr">
         <is>
+          <t>洗面台・お風呂</t>
+        </is>
+      </c>
+      <c r="B21" s="7" t="inlineStr">
+        <is>
+          <t>排水口用の小さいブラシ</t>
+        </is>
+      </c>
+      <c r="C21" s="19" t="inlineStr">
+        <is>
+          <t>髪の毛・ぬめり取り</t>
+        </is>
+      </c>
+      <c r="D21" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E21" s="20" t="n"/>
+    </row>
+    <row r="22" ht="30" customHeight="1">
+      <c r="A22" s="8" t="inlineStr">
+        <is>
           <t>お風呂</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
-        <is>
-          <t>浴室用スポンジ・柄つきブラシ</t>
-        </is>
-      </c>
-      <c r="C21" s="19" t="inlineStr">
-        <is>
-          <t>床・壁・椅子・テーブル</t>
-        </is>
-      </c>
-      <c r="D21" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E21" s="20" t="n"/>
-    </row>
-    <row r="22" ht="20" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>お風呂</t>
-        </is>
-      </c>
       <c r="B22" s="7" t="inlineStr">
         <is>
-          <t>防カビくん煙剤</t>
+          <t>浴槽用スプレー洗剤（30秒で流すタイプ）</t>
         </is>
       </c>
       <c r="C22" s="19" t="inlineStr">
         <is>
-          <t>2か月に1回（年6個）</t>
+          <t>使用中の物</t>
         </is>
       </c>
       <c r="D22" s="20" t="inlineStr">
@@ -2002,17 +2014,17 @@
     <row r="23" ht="20" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>ホコリ取り</t>
+          <t>お風呂</t>
         </is>
       </c>
       <c r="B23" s="7" t="inlineStr">
         <is>
-          <t>ハンディモップ（替えシートも）</t>
+          <t>浴室用スポンジ・柄つきブラシ</t>
         </is>
       </c>
       <c r="C23" s="19" t="inlineStr">
         <is>
-          <t>テーブル・ベッドフレーム・台・お風呂の扉</t>
+          <t>床・壁・椅子・テーブル</t>
         </is>
       </c>
       <c r="D23" s="20" t="inlineStr">
@@ -2022,20 +2034,20 @@
       </c>
       <c r="E23" s="20" t="n"/>
     </row>
-    <row r="24" ht="30" customHeight="1">
+    <row r="24" ht="20" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>拭き掃除</t>
+          <t>お風呂</t>
         </is>
       </c>
       <c r="B24" s="7" t="inlineStr">
         <is>
-          <t>マイクロファイバークロス（数枚）</t>
+          <t>防カビくん煙剤</t>
         </is>
       </c>
       <c r="C24" s="19" t="inlineStr">
         <is>
-          <t>水拭き用・乾拭き用に分ける。ガラスのテーブル・シンク・洗面台</t>
+          <t>2か月に1回（年6個）</t>
         </is>
       </c>
       <c r="D24" s="20" t="inlineStr">
@@ -2048,128 +2060,132 @@
     <row r="25" ht="20" customHeight="1">
       <c r="A25" s="8" t="inlineStr">
         <is>
+          <t>ホコリ取り</t>
+        </is>
+      </c>
+      <c r="B25" s="7" t="inlineStr">
+        <is>
+          <t>ハンディモップ（替えシートも）</t>
+        </is>
+      </c>
+      <c r="C25" s="19" t="inlineStr">
+        <is>
+          <t>テーブル・ベッドフレーム・台・お風呂の扉</t>
+        </is>
+      </c>
+      <c r="D25" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E25" s="20" t="n"/>
+    </row>
+    <row r="26" ht="30" customHeight="1">
+      <c r="A26" s="8" t="inlineStr">
+        <is>
           <t>拭き掃除</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B26" s="7" t="inlineStr">
+        <is>
+          <t>マイクロファイバークロス（数枚）</t>
+        </is>
+      </c>
+      <c r="C26" s="19" t="inlineStr">
+        <is>
+          <t>水拭き用・乾拭き用に分ける。ガラスのテーブル・シンク・洗面台</t>
+        </is>
+      </c>
+      <c r="D26" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E26" s="20" t="n"/>
+    </row>
+    <row r="27" ht="20" customHeight="1">
+      <c r="A27" s="8" t="inlineStr">
+        <is>
+          <t>拭き掃除</t>
+        </is>
+      </c>
+      <c r="B27" s="7" t="inlineStr">
         <is>
           <t>ガラス用クリーナー</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C27" s="19" t="inlineStr">
         <is>
           <t>ガラスのテーブルの汚れがひどい時</t>
         </is>
       </c>
-      <c r="D25" s="21" t="inlineStr">
+      <c r="D27" s="21" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E25" s="20" t="n"/>
-    </row>
-    <row r="26" ht="20" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="E27" s="20" t="n"/>
+    </row>
+    <row r="28" ht="20" customHeight="1">
+      <c r="A28" s="8" t="inlineStr">
         <is>
           <t>床</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B28" s="7" t="inlineStr">
         <is>
           <t>掃除機</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C28" s="19" t="inlineStr">
         <is>
           <t>部屋と玄関</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="n"/>
-    </row>
-    <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="30" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
         <is>
           <t>床</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>クイックルワイパー（ウエットシート）</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>2週に1回</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="n"/>
-    </row>
-    <row r="28" ht="30" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="D29" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E29" s="20" t="n"/>
+    </row>
+    <row r="30" ht="30" customHeight="1">
+      <c r="A30" s="8" t="inlineStr">
         <is>
           <t>玄関</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B30" s="7" t="inlineStr">
         <is>
           <t>靴クリーム（黒用・白用）</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C30" s="19" t="inlineStr">
         <is>
           <t>月1回の靴磨き。靴の色に合わせて使い分ける</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="n"/>
-    </row>
-    <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>玄関</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>靴磨き用ブラシ・布</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr"/>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="n"/>
-    </row>
-    <row r="30" ht="20" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>消臭</t>
-        </is>
-      </c>
-      <c r="B30" s="7" t="inlineStr">
-        <is>
-          <t>布用消臭スプレー</t>
-        </is>
-      </c>
-      <c r="C30" s="19" t="inlineStr">
-        <is>
-          <t>靴・カーテン・ソファ。毎回</t>
         </is>
       </c>
       <c r="D30" s="20" t="inlineStr">
@@ -2182,19 +2198,15 @@
     <row r="31" ht="20" customHeight="1">
       <c r="A31" s="8" t="inlineStr">
         <is>
-          <t>ゴミ</t>
+          <t>玄関</t>
         </is>
       </c>
       <c r="B31" s="7" t="inlineStr">
         <is>
-          <t>名古屋市指定ごみ袋（可燃用）</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr">
-        <is>
-          <t>燃えるゴミを出す袋</t>
-        </is>
-      </c>
+          <t>靴磨き用ブラシ・布</t>
+        </is>
+      </c>
+      <c r="C31" s="19" t="inlineStr"/>
       <c r="D31" s="20" t="inlineStr">
         <is>
           <t>必須</t>
@@ -2205,17 +2217,17 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>ゴミ</t>
+          <t>消臭</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>ゴミ箱用の袋</t>
+          <t>布用消臭スプレー</t>
         </is>
       </c>
       <c r="C32" s="19" t="inlineStr">
         <is>
-          <t>袋が付いていないゴミ箱に付ける</t>
+          <t>靴・カーテン・ソファ。毎回</t>
         </is>
       </c>
       <c r="D32" s="20" t="inlineStr">
@@ -2233,17 +2245,17 @@
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>除菌シート</t>
+          <t>名古屋市指定ごみ袋（可燃用）</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>汚れたゴミ箱の中の掃除</t>
-        </is>
-      </c>
-      <c r="D33" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+          <t>燃えるゴミを出す袋</t>
+        </is>
+      </c>
+      <c r="D33" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E33" s="20" t="n"/>
@@ -2251,17 +2263,17 @@
     <row r="34" ht="20" customHeight="1">
       <c r="A34" s="8" t="inlineStr">
         <is>
-          <t>寝室</t>
+          <t>ゴミ</t>
         </is>
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>予備のシーツ・枕カバー</t>
+          <t>ゴミ箱用の袋</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>シーツ類を洗う週に交換する（予備あり）</t>
+          <t>袋が付いていないゴミ箱に付ける</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -2274,28 +2286,74 @@
     <row r="35" ht="20" customHeight="1">
       <c r="A35" s="8" t="inlineStr">
         <is>
+          <t>ゴミ</t>
+        </is>
+      </c>
+      <c r="B35" s="7" t="inlineStr">
+        <is>
+          <t>除菌シート</t>
+        </is>
+      </c>
+      <c r="C35" s="19" t="inlineStr">
+        <is>
+          <t>汚れたゴミ箱の中の掃除</t>
+        </is>
+      </c>
+      <c r="D35" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
+        </is>
+      </c>
+      <c r="E35" s="20" t="n"/>
+    </row>
+    <row r="36" ht="20" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>寝室</t>
+        </is>
+      </c>
+      <c r="B36" s="7" t="inlineStr">
+        <is>
+          <t>予備のシーツ・枕カバー</t>
+        </is>
+      </c>
+      <c r="C36" s="19" t="inlineStr">
+        <is>
+          <t>シーツ類を洗う週に交換する（予備あり）</t>
+        </is>
+      </c>
+      <c r="D36" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E36" s="20" t="n"/>
+    </row>
+    <row r="37" ht="20" customHeight="1">
+      <c r="A37" s="8" t="inlineStr">
+        <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B37" s="7" t="inlineStr">
         <is>
           <t>ゴム手袋・使い捨て手袋</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C37" s="19" t="inlineStr">
         <is>
           <t>トイレ・お風呂・排水口・ゴミ箱</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="n"/>
-    </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="n"/>
+    </row>
+    <row r="38">
+      <c r="A38" s="11" t="inlineStr">
         <is>
           <t>※パイプユニッシュ（塩素系）と酸性の洗剤（クエン酸など）は、同じ場所に置かず、混ぜないでください。</t>
         </is>
@@ -2305,7 +2363,7 @@
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A36:E36"/>
+    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -12,9 +12,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具・洗剤リスト" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$36</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'道具・洗剤リスト'!$A$1:$E$38</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$26</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'道具・洗剤リスト'!$A$1:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -589,7 +589,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C24"/>
+  <dimension ref="A1:C26"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -618,27 +618,34 @@
         </is>
       </c>
     </row>
-    <row r="4" ht="8" customHeight="1"/>
-    <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="4" t="inlineStr">
+    <row r="4" ht="20" customHeight="1">
+      <c r="A4" s="3" t="inlineStr">
+        <is>
+          <t>作業中は依頼者が在宅しています。わからないことは、その場で声をかけてください。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="8" customHeight="1"/>
+    <row r="6" ht="22" customHeight="1">
+      <c r="A6" s="4" t="inlineStr">
         <is>
           <t>作業の流れ</t>
         </is>
       </c>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="108" customHeight="1">
-      <c r="A6" s="6" t="n">
+      <c r="B6" s="5" t="n"/>
+      <c r="C6" s="5" t="n"/>
+    </row>
+    <row r="7" ht="108" customHeight="1">
+      <c r="A7" s="6" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B7" s="7" t="inlineStr">
         <is>
           <t>洗濯機
 （最初に）</t>
         </is>
       </c>
-      <c r="C6" s="8" t="inlineStr">
+      <c r="C7" s="8" t="inlineStr">
         <is>
           <t>・始める前に、洗濯機横のフィルター2か所と乾燥フィルターにゴミがないか確認し、たまっていれば取る
 ・洗濯機を回す
@@ -649,17 +656,17 @@
         </is>
       </c>
     </row>
-    <row r="7" ht="78" customHeight="1">
-      <c r="A7" s="6" t="n">
+    <row r="8" ht="78" customHeight="1">
+      <c r="A8" s="6" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B8" s="7" t="inlineStr">
         <is>
           <t>パイプユニッシュ
 （対象の週のみ）</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
+      <c r="C8" s="8" t="inlineStr">
         <is>
           <t>・チェックリストで対象になっている週は、この時点で浴室・洗面台の排水口に入れる
 ・15〜30分たったら、たっぷりの水で流す（長時間放置しない）
@@ -668,36 +675,37 @@
         </is>
       </c>
     </row>
-    <row r="8" ht="146" customHeight="1">
-      <c r="A8" s="6" t="n">
+    <row r="9" ht="160" customHeight="1">
+      <c r="A9" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B9" s="7" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
+      <c r="C9" s="8" t="inlineStr">
         <is>
           <t>・洗い物をする。食洗機の底にたまった生ゴミを取り除く
 ・プロテインシェイカーは、こびり付いていることがあるので、スポンジでこすって泡を流してから食洗機へ
 ・ガスコンロと天板を掃除する
 ・排水口のゴミを取って捨てる（対象の週はここでパイプユニッシュを入れる）
+・月1回（対象の週）：電子レンジの中を拭く
 ・シンクは最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
 【使う道具】食器用洗剤・スポンジ、ボトルブラシ、食洗機用洗剤、コンロ用洗剤、シンク用スポンジ、排水口ネット、クロス（乾拭き用）、撥水コート剤、ゴム手袋</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="62" customHeight="1">
-      <c r="A9" s="6" t="n">
+    <row r="10" ht="62" customHeight="1">
+      <c r="A10" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B10" s="7" t="inlineStr">
         <is>
           <t>寝室</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
+      <c r="C10" s="8" t="inlineStr">
         <is>
           <t>・ベッドメイキング（シーツ類を洗う週は、予備のシーツ・枕カバーに交換し、外した物を洗濯する）
 ・ベッドフレーム、ティッシュを置いている台のホコリを取る
@@ -705,16 +713,16 @@
         </is>
       </c>
     </row>
-    <row r="10" ht="60" customHeight="1">
-      <c r="A10" s="6" t="n">
+    <row r="11" ht="60" customHeight="1">
+      <c r="A11" s="6" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B11" s="7" t="inlineStr">
         <is>
           <t>テーブル</t>
         </is>
       </c>
-      <c r="C10" s="8" t="inlineStr">
+      <c r="C11" s="8" t="inlineStr">
         <is>
           <t>・食卓のテーブル、仕事用のテーブル（ガラス）のホコリをハンディモップで取る
 ・汚れている場合は、水拭き → 乾拭き
@@ -722,32 +730,32 @@
         </is>
       </c>
     </row>
-    <row r="11" ht="40" customHeight="1">
-      <c r="A11" s="6" t="n">
+    <row r="12" ht="40" customHeight="1">
+      <c r="A12" s="6" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B12" s="7" t="inlineStr">
         <is>
           <t>トイレ</t>
         </is>
       </c>
-      <c r="C11" s="8" t="inlineStr">
+      <c r="C12" s="8" t="inlineStr">
         <is>
           <t>・トイレ掃除（掃除道具は上の棚にあります）
 【使う道具】トイレ用洗剤、トイレブラシ、トイレ掃除用シート、使い捨て手袋</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="68" customHeight="1">
-      <c r="A12" s="6" t="n">
+    <row r="13" ht="68" customHeight="1">
+      <c r="A13" s="6" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B13" s="7" t="inlineStr">
         <is>
           <t>洗面化粧台</t>
         </is>
       </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="C13" s="8" t="inlineStr">
         <is>
           <t>・ボウルをこすって掃除する
 ・排水口のゴミ・髪の毛を取って掃除する
@@ -756,16 +764,16 @@
         </is>
       </c>
     </row>
-    <row r="13" ht="174" customHeight="1">
-      <c r="A13" s="6" t="n">
+    <row r="14" ht="174" customHeight="1">
+      <c r="A14" s="6" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B14" s="7" t="inlineStr">
         <is>
           <t>お風呂</t>
         </is>
       </c>
-      <c r="C13" s="8" t="inlineStr">
+      <c r="C14" s="8" t="inlineStr">
         <is>
           <t>【毎回】
 ・浴槽：専用洗剤を吹きかけ、30秒後に流す
@@ -774,21 +782,40 @@
 ・排水口の髪の毛を取って捨てる
 ・扉のホコリを取る（通気口・枠など）
 【月1回】壁全体（手の届く範囲）、ドア、ゴムパッキンまでしっかり洗う
-【2か月に1回】掃除が終わったら防カビくん煙剤をたく（下の注意を参照）
+【2か月に1回】掃除が終わったら防カビくん煙剤をたく（下の注意を参照。雨で浴室乾燥を使う日は次の週にする）
 【使う道具】浴槽用スプレー洗剤、浴室用スポンジ・柄つきブラシ、排水口用ブラシ、ハンディモップ（扉）、防カビくん煙剤、ゴム手袋</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="112" customHeight="1">
-      <c r="A14" s="6" t="n">
+    <row r="15" ht="92" customHeight="1">
+      <c r="A15" s="6" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B15" s="7" t="inlineStr">
+        <is>
+          <t>窓・カーテン
+（季節ごと）</t>
+        </is>
+      </c>
+      <c r="C15" s="8" t="inlineStr">
+        <is>
+          <t>・対象の月の第1月曜のみ
+・窓ガラスと網戸を拭く（手の届く範囲。踏み台が必要な所は無理しない）
+・カーテンは外して、普段の洗濯とは別に洗濯機で洗う。洗い終わったら濡れたままレールに戻して乾かす
+【使う道具】ガラス用クリーナー、クロス、網戸用ブラシ（またはスポンジ）、洗濯用洗剤、洗濯ネット</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="124" customHeight="1">
+      <c r="A16" s="6" t="n">
+        <v>10</v>
+      </c>
+      <c r="B16" s="7" t="inlineStr">
         <is>
           <t>玄関・消臭</t>
         </is>
       </c>
-      <c r="C14" s="8" t="inlineStr">
+      <c r="C16" s="8" t="inlineStr">
         <is>
           <t>・出ている靴はすべて靴箱にしまう
 ・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
@@ -799,16 +826,16 @@
         </is>
       </c>
     </row>
-    <row r="15" ht="64" customHeight="1">
-      <c r="A15" s="6" t="n">
-        <v>10</v>
-      </c>
-      <c r="B15" s="7" t="inlineStr">
+    <row r="17" ht="64" customHeight="1">
+      <c r="A17" s="6" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="7" t="inlineStr">
         <is>
           <t>床・玄関</t>
         </is>
       </c>
-      <c r="C15" s="8" t="inlineStr">
+      <c r="C17" s="8" t="inlineStr">
         <is>
           <t>・毎回：部屋の床と玄関に掃除機をかける
 ・2週に1回（対象の週）：掃除機のあと、床をクイックルワイパー（ウエット）で拭く
@@ -816,49 +843,53 @@
         </is>
       </c>
     </row>
-    <row r="16" ht="68" customHeight="1">
-      <c r="A16" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>洗濯物を干す</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>・横のカゴに入れてベランダへ持っていき、干す
+    <row r="18" ht="128" customHeight="1">
+      <c r="A18" s="6" t="n">
+        <v>12</v>
+      </c>
+      <c r="B18" s="7" t="inlineStr">
+        <is>
+          <t>洗濯物</t>
+        </is>
+      </c>
+      <c r="C18" s="8" t="inlineStr">
+        <is>
+          <t>・干す前に、前回干して乾いている洗濯物を取り込む
+　ハンガーにかかっている物 → ハンガーごと押し入れにしまう
+　それ以外（ピンチハンガーの物など）→ たたまずに所定の場所（　　　　）に置く
+・今回の洗濯物を横のカゴに入れてベランダへ持っていき、干す
 ・風が強い日は、竿の下のフックにかける
-・乾燥機が終わっていれば、カゴに取り出しておく
+・雨の日：乾燥機にかけられる物は乾燥機、それ以外はお風呂に干して浴室乾燥をかける
+・乾燥機が終わっていれば取り出し、たたまずに所定の場所に置く
 【使う道具】洗濯カゴ、ピンチハンガー・ハンガー・洗濯ばさみ</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>12</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
+    <row r="19" ht="22" customHeight="1">
+      <c r="A19" s="6" t="n">
+        <v>13</v>
+      </c>
+      <c r="B19" s="7" t="inlineStr">
         <is>
           <t>洗濯機の後始末</t>
         </is>
       </c>
-      <c r="C17" s="8" t="inlineStr">
+      <c r="C19" s="8" t="inlineStr">
         <is>
           <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="150" customHeight="1">
-      <c r="A18" s="6" t="n">
-        <v>13</v>
-      </c>
-      <c r="B18" s="7" t="inlineStr">
+    <row r="20" ht="150" customHeight="1">
+      <c r="A20" s="6" t="n">
+        <v>14</v>
+      </c>
+      <c r="B20" s="7" t="inlineStr">
         <is>
           <t>ゴミ（最後に）</t>
         </is>
       </c>
-      <c r="C18" s="8" t="inlineStr">
+      <c r="C20" s="8" t="inlineStr">
         <is>
           <t>・家中のゴミ箱を集め、中身を1つの袋にまとめて燃えるゴミとして出す（量が少なくても毎回。収集は14時ごろ）
 ・ゴミ箱に袋が付いていても、袋は替えずに中身だけ移す（洗面台の鏡の中のゴミ箱の袋は月1回交換）
@@ -869,18 +900,18 @@
         </is>
       </c>
     </row>
-    <row r="19" ht="8" customHeight="1"/>
-    <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="4" t="inlineStr">
+    <row r="21" ht="8" customHeight="1"/>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="4" t="inlineStr">
         <is>
           <t>お風呂の防カビくん煙剤（2か月に1回）</t>
         </is>
       </c>
-      <c r="B20" s="5" t="n"/>
-      <c r="C20" s="5" t="n"/>
-    </row>
-    <row r="21" ht="66" customHeight="1">
-      <c r="A21" s="3" t="inlineStr">
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+    </row>
+    <row r="23" ht="66" customHeight="1">
+      <c r="A23" s="3" t="inlineStr">
         <is>
           <t>・お風呂掃除が終わってからたく。シャンプー等の置き方、濡れたままでよいか、待ち時間は、製品の説明書きに従ってください
 ・たいている間は浴室のドア・窓を閉め、換気扇を止め、浴室に入らない
@@ -888,41 +919,43 @@
         </is>
       </c>
     </row>
-    <row r="22" ht="8" customHeight="1"/>
-    <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="4" t="inlineStr">
+    <row r="24" ht="8" customHeight="1"/>
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="4" t="inlineStr">
         <is>
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B23" s="5" t="n"/>
-      <c r="C23" s="5" t="n"/>
-    </row>
-    <row r="24" ht="56" customHeight="1">
-      <c r="A24" s="9" t="inlineStr">
+      <c r="B25" s="5" t="n"/>
+      <c r="C25" s="5" t="n"/>
+    </row>
+    <row r="26" ht="72" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>・パイプユニッシュ（塩素系）は、酸性の洗剤やクエン酸と絶対に混ぜない。使っている間は換気する
 ・高い所の作業や、無理な姿勢での作業はしなくて構いません
+・作業で動かした物は、元の位置に戻してください
 ・気づいたこと、足りない洗剤などは、チェックリストの連絡事項に書いてください</t>
         </is>
       </c>
-      <c r="B24" s="5" t="n"/>
-      <c r="C24" s="5" t="n"/>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
+    <mergeCell ref="A25:C25"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A5:C5"/>
     <mergeCell ref="A23:C23"/>
+    <mergeCell ref="A6:C6"/>
+    <mergeCell ref="A22:C22"/>
     <mergeCell ref="A3:C3"/>
-    <mergeCell ref="A21:C21"/>
-    <mergeCell ref="A20:C20"/>
-    <mergeCell ref="A24:C24"/>
+    <mergeCell ref="A4:C4"/>
+    <mergeCell ref="A26:C26"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" fitToHeight="2" fitToWidth="1"/>
 </worksheet>
 </file>
 
@@ -932,7 +965,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F36"/>
+  <dimension ref="A1:F40"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -1165,7 +1198,7 @@
     <row r="18" ht="22" customHeight="1">
       <c r="A18" s="8" t="inlineStr">
         <is>
-          <t>洗濯物を干す</t>
+          <t>乾いた洗濯物の取り込み・片付け</t>
         </is>
       </c>
       <c r="B18" s="14" t="n"/>
@@ -1177,7 +1210,7 @@
     <row r="19" ht="22" customHeight="1">
       <c r="A19" s="8" t="inlineStr">
         <is>
-          <t>洗濯機のフタを開けて乾かす</t>
+          <t>洗濯物を干す（雨の日は乾燥機・浴室乾燥）</t>
         </is>
       </c>
       <c r="B19" s="14" t="n"/>
@@ -1189,7 +1222,7 @@
     <row r="20" ht="22" customHeight="1">
       <c r="A20" s="8" t="inlineStr">
         <is>
-          <t>ゴミ箱を集めて燃えるゴミ出し</t>
+          <t>洗濯機のフタを開けて乾かす</t>
         </is>
       </c>
       <c r="B20" s="14" t="n"/>
@@ -1198,60 +1231,48 @@
       <c r="E20" s="14" t="n"/>
       <c r="F20" s="14" t="n"/>
     </row>
-    <row r="21" ht="18" customHeight="1">
-      <c r="A21" s="13" t="inlineStr">
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="8" t="inlineStr">
+        <is>
+          <t>ゴミ箱を集めて燃えるゴミ出し</t>
+        </is>
+      </c>
+      <c r="B21" s="14" t="n"/>
+      <c r="C21" s="14" t="n"/>
+      <c r="D21" s="14" t="n"/>
+      <c r="E21" s="14" t="n"/>
+      <c r="F21" s="14" t="n"/>
+    </row>
+    <row r="22" ht="18" customHeight="1">
+      <c r="A22" s="13" t="inlineStr">
         <is>
           <t>【2週に1回】</t>
         </is>
       </c>
-      <c r="B21" s="5" t="n"/>
-      <c r="C21" s="5" t="n"/>
-      <c r="D21" s="5" t="n"/>
-      <c r="E21" s="5" t="n"/>
-      <c r="F21" s="5" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
-        <is>
-          <t>パイプユニッシュ（キッチン・お風呂）</t>
-        </is>
-      </c>
-      <c r="B22" s="14" t="n"/>
-      <c r="C22" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D22" s="14" t="n"/>
-      <c r="E22" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F22" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B22" s="5" t="n"/>
+      <c r="C22" s="5" t="n"/>
+      <c r="D22" s="5" t="n"/>
+      <c r="E22" s="5" t="n"/>
+      <c r="F22" s="5" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1">
       <c r="A23" s="8" t="inlineStr">
         <is>
-          <t>シーツ・枕カバーを予備に交換して洗濯</t>
-        </is>
-      </c>
-      <c r="B23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C23" s="14" t="n"/>
-      <c r="D23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E23" s="14" t="n"/>
+          <t>パイプユニッシュ（キッチン・お風呂）</t>
+        </is>
+      </c>
+      <c r="B23" s="14" t="n"/>
+      <c r="C23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="14" t="n"/>
+      <c r="E23" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F23" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1261,7 +1282,7 @@
     <row r="24" ht="22" customHeight="1">
       <c r="A24" s="8" t="inlineStr">
         <is>
-          <t>床のクイックルワイパー（ウエット）</t>
+          <t>シーツ・枕カバーを予備に交換して洗濯</t>
         </is>
       </c>
       <c r="B24" s="15" t="inlineStr">
@@ -1282,58 +1303,54 @@
         </is>
       </c>
     </row>
-    <row r="25" ht="18" customHeight="1">
-      <c r="A25" s="13" t="inlineStr">
+    <row r="25" ht="22" customHeight="1">
+      <c r="A25" s="8" t="inlineStr">
+        <is>
+          <t>床のクイックルワイパー（ウエット）</t>
+        </is>
+      </c>
+      <c r="B25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C25" s="14" t="n"/>
+      <c r="D25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E25" s="14" t="n"/>
+      <c r="F25" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="18" customHeight="1">
+      <c r="A26" s="13" t="inlineStr">
         <is>
           <t>【月1回】</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-      <c r="D25" s="5" t="n"/>
-      <c r="E25" s="5" t="n"/>
-      <c r="F25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
-        <is>
-          <t>靴磨き（黒用・白用クリームを使い分け）</t>
-        </is>
-      </c>
-      <c r="B26" s="14" t="n"/>
-      <c r="C26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F26" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
+      <c r="B26" s="5" t="n"/>
+      <c r="C26" s="5" t="n"/>
+      <c r="D26" s="5" t="n"/>
+      <c r="E26" s="5" t="n"/>
+      <c r="F26" s="5" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
-          <t>パイプユニッシュ（洗面台）</t>
-        </is>
-      </c>
-      <c r="B27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C27" s="14" t="n"/>
+          <t>靴磨き（黒用・白用クリームを使い分け）</t>
+        </is>
+      </c>
+      <c r="B27" s="14" t="n"/>
+      <c r="C27" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="D27" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1353,7 +1370,7 @@
     <row r="28" ht="22" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
-          <t>撥水コート（シンク・洗面台）</t>
+          <t>パイプユニッシュ（洗面台）</t>
         </is>
       </c>
       <c r="B28" s="15" t="inlineStr">
@@ -1361,12 +1378,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="C28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D28" s="14" t="n"/>
+      <c r="C28" s="14" t="n"/>
+      <c r="D28" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="E28" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1381,7 +1398,7 @@
     <row r="29" ht="22" customHeight="1">
       <c r="A29" s="8" t="inlineStr">
         <is>
-          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
+          <t>撥水コート（シンク・洗面台）</t>
         </is>
       </c>
       <c r="B29" s="15" t="inlineStr">
@@ -1394,12 +1411,12 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E29" s="14" t="n"/>
+      <c r="D29" s="14" t="n"/>
+      <c r="E29" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F29" s="15" t="inlineStr">
         <is>
           <t>—</t>
@@ -1409,7 +1426,7 @@
     <row r="30" ht="22" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
-          <t>洗面台ゴミ箱の袋交換</t>
+          <t>電子レンジの中を拭く</t>
         </is>
       </c>
       <c r="B30" s="15" t="inlineStr">
@@ -1422,34 +1439,50 @@
           <t>—</t>
         </is>
       </c>
-      <c r="D30" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E30" s="14" t="n"/>
+      <c r="D30" s="14" t="n"/>
+      <c r="E30" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
       <c r="F30" s="15" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="18" customHeight="1">
-      <c r="A31" s="13" t="inlineStr">
-        <is>
-          <t>【2か月に1回（　　月・　　月・　　月…）】</t>
-        </is>
-      </c>
-      <c r="B31" s="5" t="n"/>
-      <c r="C31" s="5" t="n"/>
-      <c r="D31" s="5" t="n"/>
-      <c r="E31" s="5" t="n"/>
-      <c r="F31" s="5" t="n"/>
+    <row r="31" ht="22" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
+          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
+        </is>
+      </c>
+      <c r="B31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="14" t="n"/>
+      <c r="F31" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="32" ht="22" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>お風呂の防カビくん煙剤（対象月のみ）</t>
+          <t>洗面台ゴミ箱の袋交換</t>
         </is>
       </c>
       <c r="B32" s="15" t="inlineStr">
@@ -1474,10 +1507,10 @@
         </is>
       </c>
     </row>
-    <row r="33" ht="30" customHeight="1">
-      <c r="A33" s="16" t="inlineStr">
-        <is>
-          <t>作業時間（開始〜終了）</t>
+    <row r="33" ht="18" customHeight="1">
+      <c r="A33" s="13" t="inlineStr">
+        <is>
+          <t>【2か月に1回（　　月・　　月・　　月…）】</t>
         </is>
       </c>
       <c r="B33" s="5" t="n"/>
@@ -1486,22 +1519,38 @@
       <c r="E33" s="5" t="n"/>
       <c r="F33" s="5" t="n"/>
     </row>
-    <row r="34" ht="26" customHeight="1">
-      <c r="A34" s="16" t="inlineStr">
-        <is>
-          <t>作業員サイン</t>
-        </is>
-      </c>
-      <c r="B34" s="5" t="n"/>
-      <c r="C34" s="5" t="n"/>
-      <c r="D34" s="5" t="n"/>
-      <c r="E34" s="5" t="n"/>
-      <c r="F34" s="5" t="n"/>
-    </row>
-    <row r="35" ht="70" customHeight="1">
-      <c r="A35" s="16" t="inlineStr">
-        <is>
-          <t>連絡事項</t>
+    <row r="34" ht="22" customHeight="1">
+      <c r="A34" s="8" t="inlineStr">
+        <is>
+          <t>お風呂の防カビくん煙剤（対象月のみ）</t>
+        </is>
+      </c>
+      <c r="B34" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C34" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D34" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E34" s="14" t="n"/>
+      <c r="F34" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="35" ht="18" customHeight="1">
+      <c r="A35" s="13" t="inlineStr">
+        <is>
+          <t>【季節ごと（　　月・　　月・　　月・　　月）】</t>
         </is>
       </c>
       <c r="B35" s="5" t="n"/>
@@ -1510,22 +1559,87 @@
       <c r="E35" s="5" t="n"/>
       <c r="F35" s="5" t="n"/>
     </row>
-    <row r="36">
-      <c r="A36" s="11" t="inlineStr">
+    <row r="36" ht="22" customHeight="1">
+      <c r="A36" s="8" t="inlineStr">
+        <is>
+          <t>窓・網戸の拭き掃除、カーテンの洗濯（対象月のみ）</t>
+        </is>
+      </c>
+      <c r="B36" s="14" t="n"/>
+      <c r="C36" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D36" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E36" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F36" s="15" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="37" ht="30" customHeight="1">
+      <c r="A37" s="16" t="inlineStr">
+        <is>
+          <t>作業時間（開始〜終了）</t>
+        </is>
+      </c>
+      <c r="B37" s="5" t="n"/>
+      <c r="C37" s="5" t="n"/>
+      <c r="D37" s="5" t="n"/>
+      <c r="E37" s="5" t="n"/>
+      <c r="F37" s="5" t="n"/>
+    </row>
+    <row r="38" ht="26" customHeight="1">
+      <c r="A38" s="16" t="inlineStr">
+        <is>
+          <t>作業員サイン</t>
+        </is>
+      </c>
+      <c r="B38" s="5" t="n"/>
+      <c r="C38" s="5" t="n"/>
+      <c r="D38" s="5" t="n"/>
+      <c r="E38" s="5" t="n"/>
+      <c r="F38" s="5" t="n"/>
+    </row>
+    <row r="39" ht="70" customHeight="1">
+      <c r="A39" s="16" t="inlineStr">
+        <is>
+          <t>連絡事項</t>
+        </is>
+      </c>
+      <c r="B39" s="5" t="n"/>
+      <c r="C39" s="5" t="n"/>
+      <c r="D39" s="5" t="n"/>
+      <c r="E39" s="5" t="n"/>
+      <c r="F39" s="5" t="n"/>
+    </row>
+    <row r="40">
+      <c r="A40" s="11" t="inlineStr">
         <is>
           <t>※第5月曜がない月は、第5月曜の欄は使いません。作業の詳しい手順は「作業手順書」を見てください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="7">
+  <mergeCells count="8">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A36:F36"/>
+    <mergeCell ref="A33:F33"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A31:F31"/>
+    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A40:F40"/>
+    <mergeCell ref="A35:F35"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A21:F21"/>
-    <mergeCell ref="A25:F25"/>
+    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1539,7 +1653,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:E38"/>
+  <dimension ref="A1:E39"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -1622,7 +1736,7 @@
       </c>
       <c r="C5" s="19" t="inlineStr">
         <is>
-          <t>ボクサーパンツなど傷みやすい物</t>
+          <t>ボクサーパンツなど傷みやすい物、カーテン</t>
         </is>
       </c>
       <c r="D5" s="21" t="inlineStr">
@@ -2103,7 +2217,7 @@
       </c>
       <c r="E26" s="20" t="n"/>
     </row>
-    <row r="27" ht="20" customHeight="1">
+    <row r="27" ht="30" customHeight="1">
       <c r="A27" s="8" t="inlineStr">
         <is>
           <t>拭き掃除</t>
@@ -2116,12 +2230,12 @@
       </c>
       <c r="C27" s="19" t="inlineStr">
         <is>
-          <t>ガラスのテーブルの汚れがひどい時</t>
-        </is>
-      </c>
-      <c r="D27" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+          <t>窓ガラス（季節ごと）。ガラスのテーブルの汚れがひどい時</t>
+        </is>
+      </c>
+      <c r="D27" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E27" s="20" t="n"/>
@@ -2129,40 +2243,40 @@
     <row r="28" ht="20" customHeight="1">
       <c r="A28" s="8" t="inlineStr">
         <is>
+          <t>窓</t>
+        </is>
+      </c>
+      <c r="B28" s="7" t="inlineStr">
+        <is>
+          <t>網戸用ブラシ（またはスポンジ）</t>
+        </is>
+      </c>
+      <c r="C28" s="19" t="inlineStr">
+        <is>
+          <t>網戸の拭き掃除（季節ごと）</t>
+        </is>
+      </c>
+      <c r="D28" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E28" s="20" t="n"/>
+    </row>
+    <row r="29" ht="20" customHeight="1">
+      <c r="A29" s="8" t="inlineStr">
+        <is>
           <t>床</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B29" s="7" t="inlineStr">
         <is>
           <t>掃除機</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C29" s="19" t="inlineStr">
         <is>
           <t>部屋と玄関</t>
-        </is>
-      </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="n"/>
-    </row>
-    <row r="29" ht="30" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>床</t>
-        </is>
-      </c>
-      <c r="B29" s="7" t="inlineStr">
-        <is>
-          <t>クイックルワイパー（ウエットシート）</t>
-        </is>
-      </c>
-      <c r="C29" s="19" t="inlineStr">
-        <is>
-          <t>2週に1回</t>
         </is>
       </c>
       <c r="D29" s="20" t="inlineStr">
@@ -2175,38 +2289,42 @@
     <row r="30" ht="30" customHeight="1">
       <c r="A30" s="8" t="inlineStr">
         <is>
+          <t>床</t>
+        </is>
+      </c>
+      <c r="B30" s="7" t="inlineStr">
+        <is>
+          <t>クイックルワイパー（ウエットシート）</t>
+        </is>
+      </c>
+      <c r="C30" s="19" t="inlineStr">
+        <is>
+          <t>2週に1回</t>
+        </is>
+      </c>
+      <c r="D30" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E30" s="20" t="n"/>
+    </row>
+    <row r="31" ht="30" customHeight="1">
+      <c r="A31" s="8" t="inlineStr">
+        <is>
           <t>玄関</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B31" s="7" t="inlineStr">
         <is>
           <t>靴クリーム（黒用・白用）</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C31" s="19" t="inlineStr">
         <is>
           <t>月1回の靴磨き。靴の色に合わせて使い分ける</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="n"/>
-    </row>
-    <row r="31" ht="20" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>玄関</t>
-        </is>
-      </c>
-      <c r="B31" s="7" t="inlineStr">
-        <is>
-          <t>靴磨き用ブラシ・布</t>
-        </is>
-      </c>
-      <c r="C31" s="19" t="inlineStr"/>
       <c r="D31" s="20" t="inlineStr">
         <is>
           <t>必須</t>
@@ -2217,19 +2335,15 @@
     <row r="32" ht="20" customHeight="1">
       <c r="A32" s="8" t="inlineStr">
         <is>
-          <t>消臭</t>
+          <t>玄関</t>
         </is>
       </c>
       <c r="B32" s="7" t="inlineStr">
         <is>
-          <t>布用消臭スプレー</t>
-        </is>
-      </c>
-      <c r="C32" s="19" t="inlineStr">
-        <is>
-          <t>靴・カーテン・ソファ。毎回</t>
-        </is>
-      </c>
+          <t>靴磨き用ブラシ・布</t>
+        </is>
+      </c>
+      <c r="C32" s="19" t="inlineStr"/>
       <c r="D32" s="20" t="inlineStr">
         <is>
           <t>必須</t>
@@ -2240,17 +2354,17 @@
     <row r="33" ht="20" customHeight="1">
       <c r="A33" s="8" t="inlineStr">
         <is>
-          <t>ゴミ</t>
+          <t>消臭</t>
         </is>
       </c>
       <c r="B33" s="7" t="inlineStr">
         <is>
-          <t>名古屋市指定ごみ袋（可燃用）</t>
+          <t>布用消臭スプレー</t>
         </is>
       </c>
       <c r="C33" s="19" t="inlineStr">
         <is>
-          <t>燃えるゴミを出す袋</t>
+          <t>靴・カーテン・ソファ。毎回</t>
         </is>
       </c>
       <c r="D33" s="20" t="inlineStr">
@@ -2268,12 +2382,12 @@
       </c>
       <c r="B34" s="7" t="inlineStr">
         <is>
-          <t>ゴミ箱用の袋</t>
+          <t>名古屋市指定ごみ袋（可燃用）</t>
         </is>
       </c>
       <c r="C34" s="19" t="inlineStr">
         <is>
-          <t>袋が付いていないゴミ箱に付ける</t>
+          <t>燃えるゴミを出す袋</t>
         </is>
       </c>
       <c r="D34" s="20" t="inlineStr">
@@ -2291,17 +2405,17 @@
       </c>
       <c r="B35" s="7" t="inlineStr">
         <is>
-          <t>除菌シート</t>
+          <t>ゴミ箱用の袋</t>
         </is>
       </c>
       <c r="C35" s="19" t="inlineStr">
         <is>
-          <t>汚れたゴミ箱の中の掃除</t>
-        </is>
-      </c>
-      <c r="D35" s="21" t="inlineStr">
-        <is>
-          <t>あると便利</t>
+          <t>袋が付いていないゴミ箱に付ける</t>
+        </is>
+      </c>
+      <c r="D35" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
         </is>
       </c>
       <c r="E35" s="20" t="n"/>
@@ -2309,22 +2423,22 @@
     <row r="36" ht="20" customHeight="1">
       <c r="A36" s="8" t="inlineStr">
         <is>
-          <t>寝室</t>
+          <t>ゴミ</t>
         </is>
       </c>
       <c r="B36" s="7" t="inlineStr">
         <is>
-          <t>予備のシーツ・枕カバー</t>
+          <t>除菌シート</t>
         </is>
       </c>
       <c r="C36" s="19" t="inlineStr">
         <is>
-          <t>シーツ類を洗う週に交換する（予備あり）</t>
-        </is>
-      </c>
-      <c r="D36" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
+          <t>汚れたゴミ箱の中の掃除</t>
+        </is>
+      </c>
+      <c r="D36" s="21" t="inlineStr">
+        <is>
+          <t>あると便利</t>
         </is>
       </c>
       <c r="E36" s="20" t="n"/>
@@ -2332,28 +2446,51 @@
     <row r="37" ht="20" customHeight="1">
       <c r="A37" s="8" t="inlineStr">
         <is>
+          <t>寝室</t>
+        </is>
+      </c>
+      <c r="B37" s="7" t="inlineStr">
+        <is>
+          <t>予備のシーツ・枕カバー</t>
+        </is>
+      </c>
+      <c r="C37" s="19" t="inlineStr">
+        <is>
+          <t>シーツ類を洗う週に交換する（予備あり）</t>
+        </is>
+      </c>
+      <c r="D37" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E37" s="20" t="n"/>
+    </row>
+    <row r="38" ht="20" customHeight="1">
+      <c r="A38" s="8" t="inlineStr">
+        <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B38" s="7" t="inlineStr">
         <is>
           <t>ゴム手袋・使い捨て手袋</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C38" s="19" t="inlineStr">
         <is>
           <t>トイレ・お風呂・排水口・ゴミ箱</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="n"/>
-    </row>
-    <row r="38">
-      <c r="A38" s="11" t="inlineStr">
+      <c r="D38" s="20" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E38" s="20" t="n"/>
+    </row>
+    <row r="39">
+      <c r="A39" s="11" t="inlineStr">
         <is>
           <t>※パイプユニッシュ（塩素系）と酸性の洗剤（クエン酸など）は、同じ場所に置かず、混ぜないでください。</t>
         </is>
@@ -2362,8 +2499,8 @@
   </sheetData>
   <mergeCells count="3">
     <mergeCell ref="A2:E2"/>
+    <mergeCell ref="A39:E39"/>
     <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A38:E38"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>

--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -856,11 +856,11 @@
         <is>
           <t>・干す前に、前回干して乾いている洗濯物を取り込む
 　ハンガーにかかっている物 → ハンガーごと押し入れにしまう
-　それ以外（ピンチハンガーの物など）→ たたまずに所定の場所（　　　　）に置く
+　それ以外（ピンチハンガーの物など）→ たたまずに寝室の赤いカゴの中に置く
 ・今回の洗濯物を横のカゴに入れてベランダへ持っていき、干す
 ・風が強い日は、竿の下のフックにかける
 ・雨の日：乾燥機にかけられる物は乾燥機、それ以外はお風呂に干して浴室乾燥をかける
-・乾燥機が終わっていれば取り出し、たたまずに所定の場所に置く
+・乾燥機が終わっていれば取り出し、たたまずに寝室の赤いカゴの中に置く
 【使う道具】洗濯カゴ、ピンチハンガー・ハンガー・洗濯ばさみ</t>
         </is>
       </c>

--- a/家事代行_作業手順書.xlsx
+++ b/家事代行_作業手順書.xlsx
@@ -12,8 +12,8 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="道具・洗剤リスト" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$26</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$40</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'作業手順書'!$A$1:$C$25</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'チェックリスト'!$A$1:$F$47</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'道具・洗剤リスト'!$A$1:$E$39</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -23,7 +23,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="8">
+  <fonts count="10">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -64,6 +64,17 @@
       <color rgb="00808080"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="游ゴシック"/>
+      <b val="1"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="游ゴシック"/>
+      <i val="1"/>
+      <color rgb="00808080"/>
+      <sz val="9"/>
+    </font>
   </fonts>
   <fills count="6">
     <fill>
@@ -74,17 +85,17 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="00F2F2F2"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="00D9E1F2"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="00FCE4D6"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="00F2F2F2"/>
       </patternFill>
     </fill>
     <fill>
@@ -163,7 +174,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="22">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
@@ -171,13 +182,16 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -187,17 +201,17 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -206,17 +220,24 @@
     <xf numFmtId="0" fontId="7" fillId="5" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="4" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -589,7 +610,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:C26"/>
+  <dimension ref="A1:C25"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="5" customWidth="1" min="1" max="1"/>
@@ -611,307 +632,293 @@
         </is>
       </c>
     </row>
-    <row r="3" ht="30" customHeight="1">
+    <row r="3" ht="44" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>下の順番で進めると、待ち時間（洗濯・パイプユニッシュ）を有効に使えます。終わった作業は「チェックリスト」に○をつけてください。</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="3" t="inlineStr">
-        <is>
-          <t>作業中は依頼者が在宅しています。わからないことは、その場で声をかけてください。</t>
+          <t>【順番の考え方】①時間のかかる物（洗濯・パイプユニッシュ）を最初に始める　②ホコリは上から落ちるので、乾いたホコリ取りを先に、床は最後　③水回りはきれいな所から（キッチン→洗面→お風呂→トイレ）　④同じ道具を使う作業を続けて行い、道具の持ち替えを少なくする</t>
+        </is>
+      </c>
+      <c r="B3" s="4" t="n"/>
+      <c r="C3" s="4" t="n"/>
+    </row>
+    <row r="4" ht="32" customHeight="1">
+      <c r="A4" s="5" t="inlineStr">
+        <is>
+          <t>・終わった作業は「チェックリスト」に○をつけてください
+・作業中は依頼者が在宅しています。わからないことは、その場で声をかけてください</t>
         </is>
       </c>
     </row>
     <row r="5" ht="8" customHeight="1"/>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="4" t="inlineStr">
+      <c r="A6" s="6" t="inlineStr">
         <is>
           <t>作業の流れ</t>
         </is>
       </c>
-      <c r="B6" s="5" t="n"/>
-      <c r="C6" s="5" t="n"/>
-    </row>
-    <row r="7" ht="108" customHeight="1">
-      <c r="A7" s="6" t="n">
+      <c r="B6" s="4" t="n"/>
+      <c r="C6" s="4" t="n"/>
+    </row>
+    <row r="7" ht="182" customHeight="1">
+      <c r="A7" s="7" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="7" t="inlineStr">
-        <is>
-          <t>洗濯機
+      <c r="B7" s="8" t="inlineStr">
+        <is>
+          <t>洗濯の準備
 （最初に）</t>
         </is>
       </c>
-      <c r="C7" s="8" t="inlineStr">
-        <is>
-          <t>・始める前に、洗濯機横のフィルター2か所と乾燥フィルターにゴミがないか確認し、たまっていれば取る
-・洗濯機を回す
-・乾燥機にかけるもの：タオル、靴下など
-・乾燥機にかけないもの：ボクサーパンツ（必ず干す）、その他の衣類
+      <c r="C7" s="9" t="inlineStr">
+        <is>
+          <t>・前回干して乾いている洗濯物を取り込む（竿を空けるため）
+　ハンガーの物 → ハンガーごと押し入れにしまう／それ以外 → たたまずに寝室の赤いカゴの中に置く
+・シーツ類を洗う週は、ベッドのシーツ・枕カバーを外して洗濯物に入れる
+・洗濯機横のフィルター2か所と乾燥フィルターのゴミを取ってから、洗濯機を回す
+・乾燥機にかけないもの：ボクサーパンツ（必ず干す）。乾燥機にかけるもの：タオル、靴下など
+・窓・カーテンの月は、カーテンを外しておく（普段の洗濯が終わってから別に洗う）
 ※洗濯機のフタが壊れています。開け閉めはゆっくり注意して行ってください
 【使う道具】洗濯用洗剤、洗濯ネット、古歯ブラシ（フィルター）</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="78" customHeight="1">
-      <c r="A8" s="6" t="n">
+    <row r="8" ht="66" customHeight="1">
+      <c r="A8" s="7" t="n">
         <v>2</v>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>パイプユニッシュ
 （対象の週のみ）</t>
         </is>
       </c>
-      <c r="C8" s="8" t="inlineStr">
-        <is>
-          <t>・チェックリストで対象になっている週は、この時点で浴室・洗面台の排水口に入れる
-・15〜30分たったら、たっぷりの水で流す（長時間放置しない）
-・キッチンは、洗い物が終わってから入れる（手順3）
+      <c r="C8" s="9" t="inlineStr">
+        <is>
+          <t>・洗面台・お風呂の排水口に入れる（流すのは手順5・6の最初）
+・キッチンは洗い物が終わってから入れる（手順4）
+・入れてから15〜30分で水で流す。長時間放置しない
 【使う道具】パイプユニッシュ、ゴム手袋</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="160" customHeight="1">
-      <c r="A9" s="6" t="n">
+    <row r="9" ht="172" customHeight="1">
+      <c r="A9" s="7" t="n">
         <v>3</v>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
+        <is>
+          <t>ホコリ取り・寝室
+（乾いた道具で一巡）</t>
+        </is>
+      </c>
+      <c r="C9" s="9" t="inlineStr">
+        <is>
+          <t>ハンディモップを持って、次の順に回る
+・寝室：ベッドフレーム、ティッシュを置いている台 → ベッドメイキング（シーツ類を洗う週は予備に交換）
+・テーブル：食卓、仕事用のガラスのテーブル。汚れていれば水拭き → 乾拭き
+・窓・カーテンの月：続けて窓ガラスと網戸を拭く（手の届く範囲）
+・お風呂の扉のホコリ（通気口・枠など）。濡らす前に取る
+・カーテン、ソファなどの布製品に消臭スプレー（革・シルクなど表示で使えない素材は除く）
+【使う道具】ハンディモップ、クロス（水拭き用・乾拭き用）、ガラス用クリーナー、網戸用ブラシ、予備のシーツ・枕カバー、布用消臭スプレー</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="134" customHeight="1">
+      <c r="A10" s="7" t="n">
+        <v>4</v>
+      </c>
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="C9" s="8" t="inlineStr">
-        <is>
-          <t>・洗い物をする。食洗機の底にたまった生ゴミを取り除く
-・プロテインシェイカーは、こびり付いていることがあるので、スポンジでこすって泡を流してから食洗機へ
+      <c r="C10" s="9" t="inlineStr">
+        <is>
+          <t>・洗い物。プロテインシェイカーはスポンジでこすって泡を流してから食洗機へ
+・食洗機の底にたまった生ゴミを取り除く
 ・ガスコンロと天板を掃除する
-・排水口のゴミを取って捨てる（対象の週はここでパイプユニッシュを入れる）
 ・月1回（対象の週）：電子レンジの中を拭く
-・シンクは最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
-【使う道具】食器用洗剤・スポンジ、ボトルブラシ、食洗機用洗剤、コンロ用洗剤、シンク用スポンジ、排水口ネット、クロス（乾拭き用）、撥水コート剤、ゴム手袋</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="62" customHeight="1">
-      <c r="A10" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="B10" s="7" t="inlineStr">
-        <is>
-          <t>寝室</t>
-        </is>
-      </c>
-      <c r="C10" s="8" t="inlineStr">
-        <is>
-          <t>・ベッドメイキング（シーツ類を洗う週は、予備のシーツ・枕カバーに交換し、外した物を洗濯する）
-・ベッドフレーム、ティッシュを置いている台のホコリを取る
-【使う道具】予備のシーツ・枕カバー、ハンディモップ</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="60" customHeight="1">
-      <c r="A11" s="6" t="n">
+・排水口のゴミを取って捨てる → 対象の週はパイプユニッシュを入れる（流すのは手順7）
+【使う道具】ゴム手袋、食器用洗剤・スポンジ、ボトルブラシ、食洗機用洗剤、コンロ用洗剤、クロス、排水口ネット、パイプユニッシュ</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="88" customHeight="1">
+      <c r="A11" s="7" t="n">
         <v>5</v>
       </c>
-      <c r="B11" s="7" t="inlineStr">
-        <is>
-          <t>テーブル</t>
-        </is>
-      </c>
-      <c r="C11" s="8" t="inlineStr">
-        <is>
-          <t>・食卓のテーブル、仕事用のテーブル（ガラス）のホコリをハンディモップで取る
-・汚れている場合は、水拭き → 乾拭き
-【使う道具】ハンディモップ、クロス（水拭き用・乾拭き用）、ガラス用クリーナー（汚れがひどい時）</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="40" customHeight="1">
-      <c r="A12" s="6" t="n">
+      <c r="B11" s="8" t="inlineStr">
+        <is>
+          <t>洗面化粧台</t>
+        </is>
+      </c>
+      <c r="C11" s="9" t="inlineStr">
+        <is>
+          <t>・対象の週は、最初にパイプユニッシュを水で流す
+・ボウルをこすって掃除する → 排水口のゴミ・髪の毛を取って掃除する
+・乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
+【使う道具】ゴム手袋、洗面台用スポンジ、排水口用ブラシ、クロス（乾拭き用）、撥水コート剤</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="156" customHeight="1">
+      <c r="A12" s="7" t="n">
         <v>6</v>
       </c>
-      <c r="B12" s="7" t="inlineStr">
-        <is>
-          <t>トイレ</t>
-        </is>
-      </c>
-      <c r="C12" s="8" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
+        <is>
+          <t>お風呂</t>
+        </is>
+      </c>
+      <c r="C12" s="9" t="inlineStr">
+        <is>
+          <t>・対象の週は、最初にパイプユニッシュを水で流す
+・浴槽に専用洗剤を吹きかけ、30秒待つ間に椅子・シャンプーを置いているテーブルを洗う（ボトルの底のぬめりも）→ 浴槽を流す
+・床、壁（手の届く低い所）を洗う → 排水口の髪の毛を取って捨てる
+・月1回（対象の週）：壁全体（手の届く範囲）、ドア、ゴムパッキンまでしっかり洗う
+・くん煙剤の月（第4月曜）：掃除が終わったらくん煙剤をたく（下の注意を参照）
+【使う道具】ゴム手袋、排水口用ブラシ（洗面台から続けて使う）、浴槽用スプレー洗剤、浴室用スポンジ・柄つきブラシ、防カビくん煙剤</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="64" customHeight="1">
+      <c r="A13" s="7" t="n">
+        <v>7</v>
+      </c>
+      <c r="B13" s="8" t="inlineStr">
+        <is>
+          <t>キッチン仕上げ</t>
+        </is>
+      </c>
+      <c r="C13" s="9" t="inlineStr">
+        <is>
+          <t>・対象の週は、パイプユニッシュを水で流す
+・シンクを乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート。手順5と同じ撥水コート剤）
+【使う道具】クロス（乾拭き用）、撥水コート剤</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="64" customHeight="1">
+      <c r="A14" s="7" t="n">
+        <v>8</v>
+      </c>
+      <c r="B14" s="8" t="inlineStr">
+        <is>
+          <t>トイレ
+（水回りの最後）</t>
+        </is>
+      </c>
+      <c r="C14" s="9" t="inlineStr">
         <is>
           <t>・トイレ掃除（掃除道具は上の棚にあります）
-【使う道具】トイレ用洗剤、トイレブラシ、トイレ掃除用シート、使い捨て手袋</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="68" customHeight="1">
-      <c r="A13" s="6" t="n">
-        <v>7</v>
-      </c>
-      <c r="B13" s="7" t="inlineStr">
-        <is>
-          <t>洗面化粧台</t>
-        </is>
-      </c>
-      <c r="C13" s="8" t="inlineStr">
-        <is>
-          <t>・ボウルをこすって掃除する
-・排水口のゴミ・髪の毛を取って掃除する
-・最後に乾拭きする（月1回の対象の週は、乾拭きのあと撥水コート）
-【使う道具】洗面台用スポンジ、排水口用ブラシ、クロス（乾拭き用）、撥水コート剤</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="174" customHeight="1">
-      <c r="A14" s="6" t="n">
-        <v>8</v>
-      </c>
-      <c r="B14" s="7" t="inlineStr">
-        <is>
-          <t>お風呂</t>
-        </is>
-      </c>
-      <c r="C14" s="8" t="inlineStr">
-        <is>
-          <t>【毎回】
-・浴槽：専用洗剤を吹きかけ、30秒後に流す
-・床、壁（手の届く低い所）を洗う
-・椅子、シャンプーを置いているテーブルを洗う（ボトルの底のぬめりも）
-・排水口の髪の毛を取って捨てる
-・扉のホコリを取る（通気口・枠など）
-【月1回】壁全体（手の届く範囲）、ドア、ゴムパッキンまでしっかり洗う
-【2か月に1回】掃除が終わったら防カビくん煙剤をたく（下の注意を参照。雨で浴室乾燥を使う日は次の週にする）
-【使う道具】浴槽用スプレー洗剤、浴室用スポンジ・柄つきブラシ、排水口用ブラシ、ハンディモップ（扉）、防カビくん煙剤、ゴム手袋</t>
+・トイレの道具は、ほかの場所には使わない
+【使う道具】使い捨て手袋、トイレ用洗剤、トイレブラシ、トイレ掃除用シート</t>
         </is>
       </c>
     </row>
     <row r="15" ht="92" customHeight="1">
-      <c r="A15" s="6" t="n">
+      <c r="A15" s="7" t="n">
         <v>9</v>
       </c>
-      <c r="B15" s="7" t="inlineStr">
-        <is>
-          <t>窓・カーテン
-（季節ごと）</t>
-        </is>
-      </c>
-      <c r="C15" s="8" t="inlineStr">
-        <is>
-          <t>・対象の月の第1月曜のみ
-・窓ガラスと網戸を拭く（手の届く範囲。踏み台が必要な所は無理しない）
-・カーテンは外して、普段の洗濯とは別に洗濯機で洗う。洗い終わったら濡れたままレールに戻して乾かす
-【使う道具】ガラス用クリーナー、クロス、網戸用ブラシ（またはスポンジ）、洗濯用洗剤、洗濯ネット</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="124" customHeight="1">
-      <c r="A16" s="6" t="n">
+      <c r="B15" s="8" t="inlineStr">
+        <is>
+          <t>玄関</t>
+        </is>
+      </c>
+      <c r="C15" s="9" t="inlineStr">
+        <is>
+          <t>・出ている靴はすべて靴箱にしまう
+・月1回（対象の週）：靴クリームで磨く（洗う必要はありません）。黒い靴は黒用、白い靴は白用を使い分ける（黒・白以外の色の靴は磨かずに残す）
+・靴に消臭スプレーをかける（手順3と同じスプレー）
+【使う道具】靴クリーム（黒用・白用）、靴磨き用ブラシ・布、布用消臭スプレー</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="64" customHeight="1">
+      <c r="A16" s="7" t="n">
         <v>10</v>
       </c>
-      <c r="B16" s="7" t="inlineStr">
-        <is>
-          <t>玄関・消臭</t>
-        </is>
-      </c>
-      <c r="C16" s="8" t="inlineStr">
-        <is>
-          <t>・出ている靴はすべて靴箱にしまう
-・月1回（対象の週）：靴を靴クリームで磨く（洗う必要はありません）
-　黒い靴は黒用、白い靴は白用のクリームを使い分ける（黒・白以外の色の靴は磨かずに残す）
-・毎回：靴、カーテン、ソファなどの布製品に消臭スプレーをかける
-　（革製品・シルクなど、スプレーの表示で使えない素材にはかけない）
-【使う道具】靴クリーム（黒用・白用）、靴磨き用ブラシ・布、布用消臭スプレー</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="64" customHeight="1">
-      <c r="A17" s="6" t="n">
-        <v>11</v>
-      </c>
-      <c r="B17" s="7" t="inlineStr">
-        <is>
-          <t>床・玄関</t>
-        </is>
-      </c>
-      <c r="C17" s="8" t="inlineStr">
-        <is>
-          <t>・毎回：部屋の床と玄関に掃除機をかける
+      <c r="B16" s="8" t="inlineStr">
+        <is>
+          <t>床
+（掃除の最後）</t>
+        </is>
+      </c>
+      <c r="C16" s="9" t="inlineStr">
+        <is>
+          <t>・部屋の床に掃除機をかけ、最後に玄関にかける
 ・2週に1回（対象の週）：掃除機のあと、床をクイックルワイパー（ウエット）で拭く
 【使う道具】掃除機、クイックルワイパー（ウエットシート）</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="128" customHeight="1">
-      <c r="A18" s="6" t="n">
+    <row r="17" ht="120" customHeight="1">
+      <c r="A17" s="7" t="n">
+        <v>11</v>
+      </c>
+      <c r="B17" s="8" t="inlineStr">
+        <is>
+          <t>洗濯物を干す
+（洗濯が終わり次第）</t>
+        </is>
+      </c>
+      <c r="C17" s="9" t="inlineStr">
+        <is>
+          <t>・洗濯機が止まったら、作業の区切りのよい所でこの手順を行う
+・横のカゴに入れてベランダへ持っていき、干す。風が強い日は竿の下のフックにかける
+・雨の日：乾燥機にかけられる物は乾燥機、それ以外はお風呂に干して浴室乾燥（くん煙剤は次の週にする）
+・乾燥機が終わっていれば取り出し、たたまずに寝室の赤いカゴの中に置く
+・窓・カーテンの月：カーテンを洗い、濡れたままレールに戻して乾かす
+【使う道具】洗濯カゴ、ピンチハンガー・ハンガー・洗濯ばさみ、洗濯ネット</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="26" customHeight="1">
+      <c r="A18" s="7" t="n">
         <v>12</v>
       </c>
-      <c r="B18" s="7" t="inlineStr">
-        <is>
-          <t>洗濯物</t>
-        </is>
-      </c>
-      <c r="C18" s="8" t="inlineStr">
-        <is>
-          <t>・干す前に、前回干して乾いている洗濯物を取り込む
-　ハンガーにかかっている物 → ハンガーごと押し入れにしまう
-　それ以外（ピンチハンガーの物など）→ たたまずに寝室の赤いカゴの中に置く
-・今回の洗濯物を横のカゴに入れてベランダへ持っていき、干す
-・風が強い日は、竿の下のフックにかける
-・雨の日：乾燥機にかけられる物は乾燥機、それ以外はお風呂に干して浴室乾燥をかける
-・乾燥機が終わっていれば取り出し、たたまずに寝室の赤いカゴの中に置く
-【使う道具】洗濯カゴ、ピンチハンガー・ハンガー・洗濯ばさみ</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="6" t="n">
+      <c r="B18" s="8" t="inlineStr">
+        <is>
+          <t>洗濯機の後始末</t>
+        </is>
+      </c>
+      <c r="C18" s="9" t="inlineStr">
+        <is>
+          <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="120" customHeight="1">
+      <c r="A19" s="7" t="n">
         <v>13</v>
       </c>
-      <c r="B19" s="7" t="inlineStr">
-        <is>
-          <t>洗濯機の後始末</t>
-        </is>
-      </c>
-      <c r="C19" s="8" t="inlineStr">
-        <is>
-          <t>・洗濯がすべて終わっていれば、フタを開けたままにして中を乾かす</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="150" customHeight="1">
-      <c r="A20" s="6" t="n">
-        <v>14</v>
-      </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>ゴミ（最後に）</t>
         </is>
       </c>
-      <c r="C20" s="8" t="inlineStr">
+      <c r="C19" s="9" t="inlineStr">
         <is>
           <t>・家中のゴミ箱を集め、中身を1つの袋にまとめて燃えるゴミとして出す（量が少なくても毎回。収集は14時ごろ）
-・ゴミ箱に袋が付いていても、袋は替えずに中身だけ移す（洗面台の鏡の中のゴミ箱の袋は月1回交換）
-・袋が付いていないゴミ箱には、新しい袋を付ける
-・ゴミ箱の中が汚れていたら掃除する
+・袋が付いているゴミ箱も、袋は替えずに中身だけ移す（洗面台の鏡の中のゴミ箱の袋は月1回交換）
+・袋が付いていないゴミ箱には新しい袋を付ける。中が汚れていたら掃除する
 ・燃えるゴミ以外（缶・びん・ペットボトルなど）が混ざっていたら、よけておく
-【使う道具】名古屋市指定ごみ袋（可燃用）、ゴミ箱用の袋、除菌シート、使い捨て手袋</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="8" customHeight="1"/>
-    <row r="22" ht="22" customHeight="1">
-      <c r="A22" s="4" t="inlineStr">
-        <is>
-          <t>お風呂の防カビくん煙剤（2か月に1回）</t>
-        </is>
-      </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-    </row>
-    <row r="23" ht="66" customHeight="1">
-      <c r="A23" s="3" t="inlineStr">
+【使う道具】使い捨て手袋、名古屋市指定ごみ袋（可燃用）、ゴミ箱用の袋、除菌シート</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="8" customHeight="1"/>
+    <row r="21" ht="22" customHeight="1">
+      <c r="A21" s="6" t="inlineStr">
+        <is>
+          <t>お風呂の防カビくん煙剤（2か月に1回：1・3・5・7・9・11月の第4月曜）</t>
+        </is>
+      </c>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="66" customHeight="1">
+      <c r="A22" s="5" t="inlineStr">
         <is>
           <t>・お風呂掃除が終わってからたく。シャンプー等の置き方、濡れたままでよいか、待ち時間は、製品の説明書きに従ってください
 ・たいている間は浴室のドア・窓を閉め、換気扇を止め、浴室に入らない
@@ -919,38 +926,38 @@
         </is>
       </c>
     </row>
-    <row r="24" ht="8" customHeight="1"/>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="4" t="inlineStr">
+    <row r="23" ht="8" customHeight="1"/>
+    <row r="24" ht="22" customHeight="1">
+      <c r="A24" s="6" t="inlineStr">
         <is>
           <t>注意事項</t>
         </is>
       </c>
-      <c r="B25" s="5" t="n"/>
-      <c r="C25" s="5" t="n"/>
-    </row>
-    <row r="26" ht="72" customHeight="1">
-      <c r="A26" s="9" t="inlineStr">
+      <c r="B24" s="4" t="n"/>
+      <c r="C24" s="4" t="n"/>
+    </row>
+    <row r="25" ht="72" customHeight="1">
+      <c r="A25" s="10" t="inlineStr">
         <is>
           <t>・パイプユニッシュ（塩素系）は、酸性の洗剤やクエン酸と絶対に混ぜない。使っている間は換気する
 ・高い所の作業や、無理な姿勢での作業はしなくて構いません
 ・作業で動かした物は、元の位置に戻してください
-・気づいたこと、足りない洗剤などは、チェックリストの連絡事項に書いてください</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
+・取り切れない汚れ、足りない洗剤、気づいたことは、チェックリストの備考メモに書いてください</t>
+        </is>
+      </c>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
     <mergeCell ref="A25:C25"/>
     <mergeCell ref="A1:C1"/>
-    <mergeCell ref="A23:C23"/>
     <mergeCell ref="A6:C6"/>
     <mergeCell ref="A22:C22"/>
     <mergeCell ref="A3:C3"/>
+    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A4:C4"/>
-    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="A24:C24"/>
     <mergeCell ref="A2:C2"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
@@ -965,7 +972,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F40"/>
+  <dimension ref="A1:F47"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="47" customWidth="1" min="1" max="1"/>
@@ -977,50 +984,50 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>家事代行　作業チェックリスト（　　年　　月）</t>
         </is>
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="11" t="inlineStr">
-        <is>
-          <t>毎週月曜日。作業が終わったら○をつけてください。灰色（—）の欄はその週は対象外です。</t>
+      <c r="A2" s="12" t="inlineStr">
+        <is>
+          <t>○：完了　△：一部できなかった（備考メモに書く）　灰色（—）：その週は対象外　※作業名の前の数字は手順書の番号</t>
         </is>
       </c>
     </row>
     <row r="3" ht="32" customHeight="1">
-      <c r="A3" s="12" t="inlineStr">
+      <c r="A3" s="13" t="inlineStr">
         <is>
           <t>作業内容</t>
         </is>
       </c>
-      <c r="B3" s="12" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>第1月曜
 （　/　）</t>
         </is>
       </c>
-      <c r="C3" s="12" t="inlineStr">
+      <c r="C3" s="13" t="inlineStr">
         <is>
           <t>第2月曜
 （　/　）</t>
         </is>
       </c>
-      <c r="D3" s="12" t="inlineStr">
+      <c r="D3" s="13" t="inlineStr">
         <is>
           <t>第3月曜
 （　/　）</t>
         </is>
       </c>
-      <c r="E3" s="12" t="inlineStr">
+      <c r="E3" s="13" t="inlineStr">
         <is>
           <t>第4月曜
 （　/　）</t>
         </is>
       </c>
-      <c r="F3" s="12" t="inlineStr">
+      <c r="F3" s="13" t="inlineStr">
         <is>
           <t>第5月曜
 （　/　）</t>
@@ -1028,618 +1035,686 @@
       </c>
     </row>
     <row r="4" ht="18" customHeight="1">
-      <c r="A4" s="13" t="inlineStr">
-        <is>
-          <t>【毎回】</t>
-        </is>
-      </c>
-      <c r="B4" s="5" t="n"/>
-      <c r="C4" s="5" t="n"/>
-      <c r="D4" s="5" t="n"/>
-      <c r="E4" s="5" t="n"/>
-      <c r="F4" s="5" t="n"/>
+      <c r="A4" s="14" t="inlineStr">
+        <is>
+          <t>【毎回】（手順書の順番）</t>
+        </is>
+      </c>
+      <c r="B4" s="4" t="n"/>
+      <c r="C4" s="4" t="n"/>
+      <c r="D4" s="4" t="n"/>
+      <c r="E4" s="4" t="n"/>
+      <c r="F4" s="4" t="n"/>
     </row>
     <row r="5" ht="22" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
-        <is>
-          <t>洗濯機フィルター確認（横2か所・乾燥）</t>
-        </is>
-      </c>
-      <c r="B5" s="14" t="n"/>
-      <c r="C5" s="14" t="n"/>
-      <c r="D5" s="14" t="n"/>
-      <c r="E5" s="14" t="n"/>
-      <c r="F5" s="14" t="n"/>
+      <c r="A5" s="9" t="inlineStr">
+        <is>
+          <t>1 乾いた洗濯物の取り込み・片付け</t>
+        </is>
+      </c>
+      <c r="B5" s="15" t="n"/>
+      <c r="C5" s="15" t="n"/>
+      <c r="D5" s="15" t="n"/>
+      <c r="E5" s="15" t="n"/>
+      <c r="F5" s="15" t="n"/>
     </row>
     <row r="6" ht="22" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
-        <is>
-          <t>洗濯（乾燥機／干す）</t>
-        </is>
-      </c>
-      <c r="B6" s="14" t="n"/>
-      <c r="C6" s="14" t="n"/>
-      <c r="D6" s="14" t="n"/>
-      <c r="E6" s="14" t="n"/>
-      <c r="F6" s="14" t="n"/>
+      <c r="A6" s="9" t="inlineStr">
+        <is>
+          <t>1 洗濯機フィルター確認・洗濯</t>
+        </is>
+      </c>
+      <c r="B6" s="15" t="n"/>
+      <c r="C6" s="15" t="n"/>
+      <c r="D6" s="15" t="n"/>
+      <c r="E6" s="15" t="n"/>
+      <c r="F6" s="15" t="n"/>
     </row>
     <row r="7" ht="22" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
-        <is>
-          <t>洗い物・食洗機の底の生ゴミ</t>
-        </is>
-      </c>
-      <c r="B7" s="14" t="n"/>
-      <c r="C7" s="14" t="n"/>
-      <c r="D7" s="14" t="n"/>
-      <c r="E7" s="14" t="n"/>
-      <c r="F7" s="14" t="n"/>
+      <c r="A7" s="9" t="inlineStr">
+        <is>
+          <t>3 ホコリ取り（寝室・テーブル・お風呂の扉）</t>
+        </is>
+      </c>
+      <c r="B7" s="15" t="n"/>
+      <c r="C7" s="15" t="n"/>
+      <c r="D7" s="15" t="n"/>
+      <c r="E7" s="15" t="n"/>
+      <c r="F7" s="15" t="n"/>
     </row>
     <row r="8" ht="22" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
-        <is>
-          <t>ガスコンロ・天板</t>
-        </is>
-      </c>
-      <c r="B8" s="14" t="n"/>
-      <c r="C8" s="14" t="n"/>
-      <c r="D8" s="14" t="n"/>
-      <c r="E8" s="14" t="n"/>
-      <c r="F8" s="14" t="n"/>
+      <c r="A8" s="9" t="inlineStr">
+        <is>
+          <t>3 ベッドメイキング</t>
+        </is>
+      </c>
+      <c r="B8" s="15" t="n"/>
+      <c r="C8" s="15" t="n"/>
+      <c r="D8" s="15" t="n"/>
+      <c r="E8" s="15" t="n"/>
+      <c r="F8" s="15" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
-        <is>
-          <t>キッチン排水口のゴミ・シンク乾拭き</t>
-        </is>
-      </c>
-      <c r="B9" s="14" t="n"/>
-      <c r="C9" s="14" t="n"/>
-      <c r="D9" s="14" t="n"/>
-      <c r="E9" s="14" t="n"/>
-      <c r="F9" s="14" t="n"/>
+      <c r="A9" s="9" t="inlineStr">
+        <is>
+          <t>3 消臭スプレー（カーテン・ソファ等）</t>
+        </is>
+      </c>
+      <c r="B9" s="15" t="n"/>
+      <c r="C9" s="15" t="n"/>
+      <c r="D9" s="15" t="n"/>
+      <c r="E9" s="15" t="n"/>
+      <c r="F9" s="15" t="n"/>
     </row>
     <row r="10" ht="22" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
-        <is>
-          <t>寝室（ベッドメイキング・フレーム・台のホコリ）</t>
-        </is>
-      </c>
-      <c r="B10" s="14" t="n"/>
-      <c r="C10" s="14" t="n"/>
-      <c r="D10" s="14" t="n"/>
-      <c r="E10" s="14" t="n"/>
-      <c r="F10" s="14" t="n"/>
+      <c r="A10" s="9" t="inlineStr">
+        <is>
+          <t>4 洗い物・食洗機の底の生ゴミ</t>
+        </is>
+      </c>
+      <c r="B10" s="15" t="n"/>
+      <c r="C10" s="15" t="n"/>
+      <c r="D10" s="15" t="n"/>
+      <c r="E10" s="15" t="n"/>
+      <c r="F10" s="15" t="n"/>
     </row>
     <row r="11" ht="22" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
-        <is>
-          <t>テーブル（食卓・仕事用ガラス）</t>
-        </is>
-      </c>
-      <c r="B11" s="14" t="n"/>
-      <c r="C11" s="14" t="n"/>
-      <c r="D11" s="14" t="n"/>
-      <c r="E11" s="14" t="n"/>
-      <c r="F11" s="14" t="n"/>
+      <c r="A11" s="9" t="inlineStr">
+        <is>
+          <t>4 ガスコンロ・天板・キッチン排水口</t>
+        </is>
+      </c>
+      <c r="B11" s="15" t="n"/>
+      <c r="C11" s="15" t="n"/>
+      <c r="D11" s="15" t="n"/>
+      <c r="E11" s="15" t="n"/>
+      <c r="F11" s="15" t="n"/>
     </row>
     <row r="12" ht="22" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
-        <is>
-          <t>トイレ</t>
-        </is>
-      </c>
-      <c r="B12" s="14" t="n"/>
-      <c r="C12" s="14" t="n"/>
-      <c r="D12" s="14" t="n"/>
-      <c r="E12" s="14" t="n"/>
-      <c r="F12" s="14" t="n"/>
+      <c r="A12" s="9" t="inlineStr">
+        <is>
+          <t>5 洗面台（ボウル・排水口・乾拭き）</t>
+        </is>
+      </c>
+      <c r="B12" s="15" t="n"/>
+      <c r="C12" s="15" t="n"/>
+      <c r="D12" s="15" t="n"/>
+      <c r="E12" s="15" t="n"/>
+      <c r="F12" s="15" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
-        <is>
-          <t>洗面台（ボウル・排水口・乾拭き）</t>
-        </is>
-      </c>
-      <c r="B13" s="14" t="n"/>
-      <c r="C13" s="14" t="n"/>
-      <c r="D13" s="14" t="n"/>
-      <c r="E13" s="14" t="n"/>
-      <c r="F13" s="14" t="n"/>
+      <c r="A13" s="9" t="inlineStr">
+        <is>
+          <t>6 お風呂（浴槽・椅子・台・床・壁・排水口）</t>
+        </is>
+      </c>
+      <c r="B13" s="15" t="n"/>
+      <c r="C13" s="15" t="n"/>
+      <c r="D13" s="15" t="n"/>
+      <c r="E13" s="15" t="n"/>
+      <c r="F13" s="15" t="n"/>
     </row>
     <row r="14" ht="22" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
-        <is>
-          <t>お風呂（浴槽・床・壁・椅子・台・排水口・扉）</t>
-        </is>
-      </c>
-      <c r="B14" s="14" t="n"/>
-      <c r="C14" s="14" t="n"/>
-      <c r="D14" s="14" t="n"/>
-      <c r="E14" s="14" t="n"/>
-      <c r="F14" s="14" t="n"/>
+      <c r="A14" s="9" t="inlineStr">
+        <is>
+          <t>7 シンク乾拭き</t>
+        </is>
+      </c>
+      <c r="B14" s="15" t="n"/>
+      <c r="C14" s="15" t="n"/>
+      <c r="D14" s="15" t="n"/>
+      <c r="E14" s="15" t="n"/>
+      <c r="F14" s="15" t="n"/>
     </row>
     <row r="15" ht="22" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
-        <is>
-          <t>玄関の靴をしまう</t>
-        </is>
-      </c>
-      <c r="B15" s="14" t="n"/>
-      <c r="C15" s="14" t="n"/>
-      <c r="D15" s="14" t="n"/>
-      <c r="E15" s="14" t="n"/>
-      <c r="F15" s="14" t="n"/>
+      <c r="A15" s="9" t="inlineStr">
+        <is>
+          <t>8 トイレ</t>
+        </is>
+      </c>
+      <c r="B15" s="15" t="n"/>
+      <c r="C15" s="15" t="n"/>
+      <c r="D15" s="15" t="n"/>
+      <c r="E15" s="15" t="n"/>
+      <c r="F15" s="15" t="n"/>
     </row>
     <row r="16" ht="22" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
-        <is>
-          <t>床・玄関の掃除機がけ</t>
-        </is>
-      </c>
-      <c r="B16" s="14" t="n"/>
-      <c r="C16" s="14" t="n"/>
-      <c r="D16" s="14" t="n"/>
-      <c r="E16" s="14" t="n"/>
-      <c r="F16" s="14" t="n"/>
+      <c r="A16" s="9" t="inlineStr">
+        <is>
+          <t>9 玄関の靴をしまう・靴に消臭スプレー</t>
+        </is>
+      </c>
+      <c r="B16" s="15" t="n"/>
+      <c r="C16" s="15" t="n"/>
+      <c r="D16" s="15" t="n"/>
+      <c r="E16" s="15" t="n"/>
+      <c r="F16" s="15" t="n"/>
     </row>
     <row r="17" ht="22" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
-        <is>
-          <t>消臭スプレー（靴・カーテン・ソファ等）</t>
-        </is>
-      </c>
-      <c r="B17" s="14" t="n"/>
-      <c r="C17" s="14" t="n"/>
-      <c r="D17" s="14" t="n"/>
-      <c r="E17" s="14" t="n"/>
-      <c r="F17" s="14" t="n"/>
+      <c r="A17" s="9" t="inlineStr">
+        <is>
+          <t>10 床・玄関の掃除機がけ</t>
+        </is>
+      </c>
+      <c r="B17" s="15" t="n"/>
+      <c r="C17" s="15" t="n"/>
+      <c r="D17" s="15" t="n"/>
+      <c r="E17" s="15" t="n"/>
+      <c r="F17" s="15" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
-        <is>
-          <t>乾いた洗濯物の取り込み・片付け</t>
-        </is>
-      </c>
-      <c r="B18" s="14" t="n"/>
-      <c r="C18" s="14" t="n"/>
-      <c r="D18" s="14" t="n"/>
-      <c r="E18" s="14" t="n"/>
-      <c r="F18" s="14" t="n"/>
+      <c r="A18" s="9" t="inlineStr">
+        <is>
+          <t>11 洗濯物を干す（雨の日は乾燥機・浴室乾燥）</t>
+        </is>
+      </c>
+      <c r="B18" s="15" t="n"/>
+      <c r="C18" s="15" t="n"/>
+      <c r="D18" s="15" t="n"/>
+      <c r="E18" s="15" t="n"/>
+      <c r="F18" s="15" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
-        <is>
-          <t>洗濯物を干す（雨の日は乾燥機・浴室乾燥）</t>
-        </is>
-      </c>
-      <c r="B19" s="14" t="n"/>
-      <c r="C19" s="14" t="n"/>
-      <c r="D19" s="14" t="n"/>
-      <c r="E19" s="14" t="n"/>
-      <c r="F19" s="14" t="n"/>
+      <c r="A19" s="9" t="inlineStr">
+        <is>
+          <t>12 洗濯機のフタを開けて乾かす</t>
+        </is>
+      </c>
+      <c r="B19" s="15" t="n"/>
+      <c r="C19" s="15" t="n"/>
+      <c r="D19" s="15" t="n"/>
+      <c r="E19" s="15" t="n"/>
+      <c r="F19" s="15" t="n"/>
     </row>
     <row r="20" ht="22" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
-        <is>
-          <t>洗濯機のフタを開けて乾かす</t>
-        </is>
-      </c>
-      <c r="B20" s="14" t="n"/>
-      <c r="C20" s="14" t="n"/>
-      <c r="D20" s="14" t="n"/>
-      <c r="E20" s="14" t="n"/>
-      <c r="F20" s="14" t="n"/>
-    </row>
-    <row r="21" ht="22" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
-        <is>
-          <t>ゴミ箱を集めて燃えるゴミ出し</t>
-        </is>
-      </c>
-      <c r="B21" s="14" t="n"/>
-      <c r="C21" s="14" t="n"/>
-      <c r="D21" s="14" t="n"/>
-      <c r="E21" s="14" t="n"/>
-      <c r="F21" s="14" t="n"/>
-    </row>
-    <row r="22" ht="18" customHeight="1">
-      <c r="A22" s="13" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
+        <is>
+          <t>13 ゴミ箱を集めて燃えるゴミ出し</t>
+        </is>
+      </c>
+      <c r="B20" s="15" t="n"/>
+      <c r="C20" s="15" t="n"/>
+      <c r="D20" s="15" t="n"/>
+      <c r="E20" s="15" t="n"/>
+      <c r="F20" s="15" t="n"/>
+    </row>
+    <row r="21" ht="18" customHeight="1">
+      <c r="A21" s="14" t="inlineStr">
         <is>
           <t>【2週に1回】</t>
         </is>
       </c>
-      <c r="B22" s="5" t="n"/>
-      <c r="C22" s="5" t="n"/>
-      <c r="D22" s="5" t="n"/>
-      <c r="E22" s="5" t="n"/>
-      <c r="F22" s="5" t="n"/>
+      <c r="B21" s="4" t="n"/>
+      <c r="C21" s="4" t="n"/>
+      <c r="D21" s="4" t="n"/>
+      <c r="E21" s="4" t="n"/>
+      <c r="F21" s="4" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1">
+      <c r="A22" s="9" t="inlineStr">
+        <is>
+          <t>1・3 シーツ・枕カバーを予備に交換して洗濯</t>
+        </is>
+      </c>
+      <c r="B22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C22" s="15" t="n"/>
+      <c r="D22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E22" s="15" t="n"/>
+      <c r="F22" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="23" ht="22" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
-        <is>
-          <t>パイプユニッシュ（キッチン・お風呂）</t>
-        </is>
-      </c>
-      <c r="B23" s="14" t="n"/>
-      <c r="C23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D23" s="14" t="n"/>
-      <c r="E23" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F23" s="15" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
+        <is>
+          <t>2 パイプユニッシュ（キッチン・お風呂）</t>
+        </is>
+      </c>
+      <c r="B23" s="15" t="n"/>
+      <c r="C23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D23" s="15" t="n"/>
+      <c r="E23" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F23" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="24" ht="22" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
-        <is>
-          <t>シーツ・枕カバーを予備に交換して洗濯</t>
-        </is>
-      </c>
-      <c r="B24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C24" s="14" t="n"/>
-      <c r="D24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E24" s="14" t="n"/>
-      <c r="F24" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="22" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
-        <is>
-          <t>床のクイックルワイパー（ウエット）</t>
-        </is>
-      </c>
-      <c r="B25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C25" s="14" t="n"/>
-      <c r="D25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E25" s="14" t="n"/>
-      <c r="F25" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="18" customHeight="1">
-      <c r="A26" s="13" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
+        <is>
+          <t>10 床のクイックルワイパー（ウエット）</t>
+        </is>
+      </c>
+      <c r="B24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C24" s="15" t="n"/>
+      <c r="D24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E24" s="15" t="n"/>
+      <c r="F24" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="18" customHeight="1">
+      <c r="A25" s="14" t="inlineStr">
         <is>
           <t>【月1回】</t>
         </is>
       </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="5" t="n"/>
-      <c r="F26" s="5" t="n"/>
+      <c r="B25" s="4" t="n"/>
+      <c r="C25" s="4" t="n"/>
+      <c r="D25" s="4" t="n"/>
+      <c r="E25" s="4" t="n"/>
+      <c r="F25" s="4" t="n"/>
+    </row>
+    <row r="26" ht="22" customHeight="1">
+      <c r="A26" s="9" t="inlineStr">
+        <is>
+          <t>2 パイプユニッシュ（洗面台）</t>
+        </is>
+      </c>
+      <c r="B26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C26" s="15" t="n"/>
+      <c r="D26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F26" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
     </row>
     <row r="27" ht="22" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
-        <is>
-          <t>靴磨き（黒用・白用クリームを使い分け）</t>
-        </is>
-      </c>
-      <c r="B27" s="14" t="n"/>
-      <c r="C27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E27" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F27" s="15" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
+        <is>
+          <t>4 電子レンジの中を拭く</t>
+        </is>
+      </c>
+      <c r="B27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D27" s="15" t="n"/>
+      <c r="E27" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F27" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="28" ht="22" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
-        <is>
-          <t>パイプユニッシュ（洗面台）</t>
-        </is>
-      </c>
-      <c r="B28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C28" s="14" t="n"/>
-      <c r="D28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E28" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F28" s="15" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
+        <is>
+          <t>5・7 撥水コート（洗面台・シンク）</t>
+        </is>
+      </c>
+      <c r="B28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D28" s="15" t="n"/>
+      <c r="E28" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F28" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="29" ht="22" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
-        <is>
-          <t>撥水コート（シンク・洗面台）</t>
-        </is>
-      </c>
-      <c r="B29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D29" s="14" t="n"/>
-      <c r="E29" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F29" s="15" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
+        <is>
+          <t>6 お風呂しっかり（壁全体・ドア・パッキン）</t>
+        </is>
+      </c>
+      <c r="B29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D29" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E29" s="15" t="n"/>
+      <c r="F29" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="30" ht="22" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
-        <is>
-          <t>電子レンジの中を拭く</t>
-        </is>
-      </c>
-      <c r="B30" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C30" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D30" s="14" t="n"/>
-      <c r="E30" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F30" s="15" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
+        <is>
+          <t>9 靴磨き（黒用・白用を使い分け）</t>
+        </is>
+      </c>
+      <c r="B30" s="15" t="n"/>
+      <c r="C30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E30" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F30" s="16" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
     </row>
     <row r="31" ht="22" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
-        <is>
-          <t>お風呂しっかり（壁全体・ドア・パッキン）</t>
-        </is>
-      </c>
-      <c r="B31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E31" s="14" t="n"/>
-      <c r="F31" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="32" ht="22" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
-        <is>
-          <t>洗面台ゴミ箱の袋交換</t>
-        </is>
-      </c>
-      <c r="B32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E32" s="14" t="n"/>
-      <c r="F32" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="18" customHeight="1">
-      <c r="A33" s="13" t="inlineStr">
-        <is>
-          <t>【2か月に1回（　　月・　　月・　　月…）】</t>
-        </is>
-      </c>
-      <c r="B33" s="5" t="n"/>
-      <c r="C33" s="5" t="n"/>
-      <c r="D33" s="5" t="n"/>
-      <c r="E33" s="5" t="n"/>
-      <c r="F33" s="5" t="n"/>
-    </row>
-    <row r="34" ht="22" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
-        <is>
-          <t>お風呂の防カビくん煙剤（対象月のみ）</t>
-        </is>
-      </c>
-      <c r="B34" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="C34" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D34" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E34" s="14" t="n"/>
-      <c r="F34" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="35" ht="18" customHeight="1">
-      <c r="A35" s="13" t="inlineStr">
-        <is>
-          <t>【季節ごと（　　月・　　月・　　月・　　月）】</t>
-        </is>
-      </c>
-      <c r="B35" s="5" t="n"/>
-      <c r="C35" s="5" t="n"/>
-      <c r="D35" s="5" t="n"/>
-      <c r="E35" s="5" t="n"/>
-      <c r="F35" s="5" t="n"/>
-    </row>
-    <row r="36" ht="22" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
-        <is>
-          <t>窓・網戸の拭き掃除、カーテンの洗濯（対象月のみ）</t>
-        </is>
-      </c>
-      <c r="B36" s="14" t="n"/>
-      <c r="C36" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="D36" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="E36" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-      <c r="F36" s="15" t="inlineStr">
-        <is>
-          <t>—</t>
-        </is>
-      </c>
-    </row>
-    <row r="37" ht="30" customHeight="1">
-      <c r="A37" s="16" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
+        <is>
+          <t>13 洗面台ゴミ箱の袋交換</t>
+        </is>
+      </c>
+      <c r="B31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E31" s="15" t="n"/>
+      <c r="F31" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="18" customHeight="1">
+      <c r="A32" s="14" t="inlineStr">
+        <is>
+          <t>【2か月に1回（1・3・5・7・9・11月）】</t>
+        </is>
+      </c>
+      <c r="B32" s="4" t="n"/>
+      <c r="C32" s="4" t="n"/>
+      <c r="D32" s="4" t="n"/>
+      <c r="E32" s="4" t="n"/>
+      <c r="F32" s="4" t="n"/>
+    </row>
+    <row r="33" ht="22" customHeight="1">
+      <c r="A33" s="9" t="inlineStr">
+        <is>
+          <t>6 お風呂の防カビくん煙剤</t>
+        </is>
+      </c>
+      <c r="B33" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="C33" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D33" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E33" s="15" t="n"/>
+      <c r="F33" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="34" ht="18" customHeight="1">
+      <c r="A34" s="14" t="inlineStr">
+        <is>
+          <t>【3か月に1回（3・6・9・12月）】</t>
+        </is>
+      </c>
+      <c r="B34" s="4" t="n"/>
+      <c r="C34" s="4" t="n"/>
+      <c r="D34" s="4" t="n"/>
+      <c r="E34" s="4" t="n"/>
+      <c r="F34" s="4" t="n"/>
+    </row>
+    <row r="35" ht="22" customHeight="1">
+      <c r="A35" s="9" t="inlineStr">
+        <is>
+          <t>3・11 窓・網戸の拭き掃除、カーテンの洗濯</t>
+        </is>
+      </c>
+      <c r="B35" s="15" t="n"/>
+      <c r="C35" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="D35" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="E35" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F35" s="16" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+    </row>
+    <row r="36" ht="26" customHeight="1">
+      <c r="A36" s="17" t="inlineStr">
         <is>
           <t>作業時間（開始〜終了）</t>
         </is>
       </c>
-      <c r="B37" s="5" t="n"/>
-      <c r="C37" s="5" t="n"/>
-      <c r="D37" s="5" t="n"/>
-      <c r="E37" s="5" t="n"/>
-      <c r="F37" s="5" t="n"/>
-    </row>
-    <row r="38" ht="26" customHeight="1">
-      <c r="A38" s="16" t="inlineStr">
+      <c r="B36" s="4" t="n"/>
+      <c r="C36" s="4" t="n"/>
+      <c r="D36" s="4" t="n"/>
+      <c r="E36" s="4" t="n"/>
+      <c r="F36" s="4" t="n"/>
+    </row>
+    <row r="37" ht="24" customHeight="1">
+      <c r="A37" s="17" t="inlineStr">
         <is>
           <t>作業員サイン</t>
         </is>
       </c>
-      <c r="B38" s="5" t="n"/>
-      <c r="C38" s="5" t="n"/>
-      <c r="D38" s="5" t="n"/>
-      <c r="E38" s="5" t="n"/>
-      <c r="F38" s="5" t="n"/>
-    </row>
-    <row r="39" ht="70" customHeight="1">
-      <c r="A39" s="16" t="inlineStr">
-        <is>
-          <t>連絡事項</t>
-        </is>
-      </c>
-      <c r="B39" s="5" t="n"/>
-      <c r="C39" s="5" t="n"/>
-      <c r="D39" s="5" t="n"/>
-      <c r="E39" s="5" t="n"/>
-      <c r="F39" s="5" t="n"/>
-    </row>
-    <row r="40">
-      <c r="A40" s="11" t="inlineStr">
+      <c r="B37" s="4" t="n"/>
+      <c r="C37" s="4" t="n"/>
+      <c r="D37" s="4" t="n"/>
+      <c r="E37" s="4" t="n"/>
+      <c r="F37" s="4" t="n"/>
+    </row>
+    <row r="39" ht="20" customHeight="1">
+      <c r="A39" s="18" t="inlineStr">
+        <is>
+          <t>備考メモ（取り切れない汚れ、足りない洗剤・道具、壊れている物、気づいたことなど）</t>
+        </is>
+      </c>
+      <c r="B39" s="4" t="n"/>
+      <c r="C39" s="4" t="n"/>
+      <c r="D39" s="4" t="n"/>
+      <c r="E39" s="4" t="n"/>
+      <c r="F39" s="4" t="n"/>
+    </row>
+    <row r="40" ht="18" customHeight="1">
+      <c r="A40" s="19" t="inlineStr">
+        <is>
+          <t>日付・場所</t>
+        </is>
+      </c>
+      <c r="B40" s="19" t="inlineStr">
+        <is>
+          <t>内容</t>
+        </is>
+      </c>
+      <c r="C40" s="4" t="n"/>
+      <c r="D40" s="4" t="n"/>
+      <c r="E40" s="4" t="n"/>
+      <c r="F40" s="4" t="n"/>
+    </row>
+    <row r="41" ht="26" customHeight="1">
+      <c r="A41" s="20" t="inlineStr">
+        <is>
+          <t>例）第1月曜（　/　）・トイレ</t>
+        </is>
+      </c>
+      <c r="B41" s="20" t="inlineStr">
+        <is>
+          <t>便器のフチ裏に、今ある洗剤・道具では取り切れない汚れがあります</t>
+        </is>
+      </c>
+      <c r="C41" s="20" t="n"/>
+      <c r="D41" s="20" t="n"/>
+      <c r="E41" s="20" t="n"/>
+      <c r="F41" s="20" t="n"/>
+    </row>
+    <row r="42" ht="26" customHeight="1">
+      <c r="A42" s="21" t="inlineStr"/>
+      <c r="B42" s="21" t="inlineStr"/>
+      <c r="C42" s="21" t="n"/>
+      <c r="D42" s="21" t="n"/>
+      <c r="E42" s="21" t="n"/>
+      <c r="F42" s="21" t="n"/>
+    </row>
+    <row r="43" ht="26" customHeight="1">
+      <c r="A43" s="21" t="inlineStr"/>
+      <c r="B43" s="21" t="inlineStr"/>
+      <c r="C43" s="21" t="n"/>
+      <c r="D43" s="21" t="n"/>
+      <c r="E43" s="21" t="n"/>
+      <c r="F43" s="21" t="n"/>
+    </row>
+    <row r="44" ht="26" customHeight="1">
+      <c r="A44" s="21" t="inlineStr"/>
+      <c r="B44" s="21" t="inlineStr"/>
+      <c r="C44" s="21" t="n"/>
+      <c r="D44" s="21" t="n"/>
+      <c r="E44" s="21" t="n"/>
+      <c r="F44" s="21" t="n"/>
+    </row>
+    <row r="45" ht="26" customHeight="1">
+      <c r="A45" s="21" t="inlineStr"/>
+      <c r="B45" s="21" t="inlineStr"/>
+      <c r="C45" s="21" t="n"/>
+      <c r="D45" s="21" t="n"/>
+      <c r="E45" s="21" t="n"/>
+      <c r="F45" s="21" t="n"/>
+    </row>
+    <row r="46" ht="26" customHeight="1">
+      <c r="A46" s="21" t="inlineStr"/>
+      <c r="B46" s="21" t="inlineStr"/>
+      <c r="C46" s="21" t="n"/>
+      <c r="D46" s="21" t="n"/>
+      <c r="E46" s="21" t="n"/>
+      <c r="F46" s="21" t="n"/>
+    </row>
+    <row r="47">
+      <c r="A47" s="12" t="inlineStr">
         <is>
           <t>※第5月曜がない月は、第5月曜の欄は使いません。作業の詳しい手順は「作業手順書」を見てください。</t>
         </is>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="16">
+    <mergeCell ref="B44:F44"/>
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A33:F33"/>
+    <mergeCell ref="B43:F43"/>
+    <mergeCell ref="A47:F47"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
-    <mergeCell ref="A40:F40"/>
-    <mergeCell ref="A35:F35"/>
+    <mergeCell ref="B42:F42"/>
+    <mergeCell ref="A32:F32"/>
+    <mergeCell ref="B45:F45"/>
+    <mergeCell ref="A34:F34"/>
+    <mergeCell ref="B46:F46"/>
     <mergeCell ref="A4:F4"/>
-    <mergeCell ref="A26:F26"/>
+    <mergeCell ref="A21:F21"/>
+    <mergeCell ref="A39:F39"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B41:F41"/>
+    <mergeCell ref="A25:F25"/>
   </mergeCells>
   <printOptions horizontalCentered="1"/>
   <pageMargins left="0.5" right="0.5" top="0.5" bottom="0.5" header="0.5" footer="0.5"/>
@@ -1664,833 +1739,833 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1">
-      <c r="A1" s="10" t="inlineStr">
+      <c r="A1" s="11" t="inlineStr">
         <is>
           <t>家事代行　道具・洗剤リスト</t>
         </is>
       </c>
     </row>
     <row r="2" ht="26" customHeight="1">
-      <c r="A2" s="17" t="inlineStr">
+      <c r="A2" s="22" t="inlineStr">
         <is>
           <t>「在庫」欄に、ある物は○、買う物は×をつけてください。「必要度」が「あると便利」の物は、なくても作業できます。</t>
         </is>
       </c>
     </row>
     <row r="3" ht="22" customHeight="1">
-      <c r="A3" s="18" t="inlineStr">
+      <c r="A3" s="23" t="inlineStr">
         <is>
           <t>場所</t>
         </is>
       </c>
-      <c r="B3" s="18" t="inlineStr">
+      <c r="B3" s="23" t="inlineStr">
         <is>
           <t>アイテム</t>
         </is>
       </c>
-      <c r="C3" s="18" t="inlineStr">
+      <c r="C3" s="23" t="inlineStr">
         <is>
           <t>使う作業・メモ</t>
         </is>
       </c>
-      <c r="D3" s="18" t="inlineStr">
+      <c r="D3" s="23" t="inlineStr">
         <is>
           <t>必要度</t>
         </is>
       </c>
-      <c r="E3" s="18" t="inlineStr">
+      <c r="E3" s="23" t="inlineStr">
         <is>
           <t>在庫</t>
         </is>
       </c>
     </row>
     <row r="4" ht="20" customHeight="1">
-      <c r="A4" s="8" t="inlineStr">
+      <c r="A4" s="9" t="inlineStr">
         <is>
           <t>洗濯</t>
         </is>
       </c>
-      <c r="B4" s="7" t="inlineStr">
+      <c r="B4" s="8" t="inlineStr">
         <is>
           <t>洗濯用洗剤</t>
         </is>
       </c>
-      <c r="C4" s="19" t="inlineStr"/>
-      <c r="D4" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E4" s="20" t="n"/>
+      <c r="C4" s="21" t="inlineStr"/>
+      <c r="D4" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E4" s="24" t="n"/>
     </row>
     <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="8" t="inlineStr">
+      <c r="A5" s="9" t="inlineStr">
         <is>
           <t>洗濯</t>
         </is>
       </c>
-      <c r="B5" s="7" t="inlineStr">
+      <c r="B5" s="8" t="inlineStr">
         <is>
           <t>洗濯ネット</t>
         </is>
       </c>
-      <c r="C5" s="19" t="inlineStr">
+      <c r="C5" s="21" t="inlineStr">
         <is>
           <t>ボクサーパンツなど傷みやすい物、カーテン</t>
         </is>
       </c>
-      <c r="D5" s="21" t="inlineStr">
+      <c r="D5" s="25" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E5" s="20" t="n"/>
+      <c r="E5" s="24" t="n"/>
     </row>
     <row r="6" ht="30" customHeight="1">
-      <c r="A6" s="8" t="inlineStr">
+      <c r="A6" s="9" t="inlineStr">
         <is>
           <t>洗濯</t>
         </is>
       </c>
-      <c r="B6" s="7" t="inlineStr">
+      <c r="B6" s="8" t="inlineStr">
         <is>
           <t>ピンチハンガー・ハンガー・洗濯ばさみ</t>
         </is>
       </c>
-      <c r="C6" s="19" t="inlineStr">
+      <c r="C6" s="21" t="inlineStr">
         <is>
           <t>干す用</t>
         </is>
       </c>
-      <c r="D6" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E6" s="20" t="n"/>
+      <c r="D6" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E6" s="24" t="n"/>
     </row>
     <row r="7" ht="20" customHeight="1">
-      <c r="A7" s="8" t="inlineStr">
+      <c r="A7" s="9" t="inlineStr">
         <is>
           <t>洗濯</t>
         </is>
       </c>
-      <c r="B7" s="7" t="inlineStr">
+      <c r="B7" s="8" t="inlineStr">
         <is>
           <t>洗濯カゴ</t>
         </is>
       </c>
-      <c r="C7" s="19" t="inlineStr">
+      <c r="C7" s="21" t="inlineStr">
         <is>
           <t>洗濯機の横にあり。ベランダに運ぶ</t>
         </is>
       </c>
-      <c r="D7" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E7" s="20" t="n"/>
+      <c r="D7" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E7" s="24" t="n"/>
     </row>
     <row r="8" ht="20" customHeight="1">
-      <c r="A8" s="8" t="inlineStr">
+      <c r="A8" s="9" t="inlineStr">
         <is>
           <t>洗濯</t>
         </is>
       </c>
-      <c r="B8" s="7" t="inlineStr">
+      <c r="B8" s="8" t="inlineStr">
         <is>
           <t>古歯ブラシ</t>
         </is>
       </c>
-      <c r="C8" s="19" t="inlineStr">
+      <c r="C8" s="21" t="inlineStr">
         <is>
           <t>洗濯機フィルターのゴミ取り</t>
         </is>
       </c>
-      <c r="D8" s="21" t="inlineStr">
+      <c r="D8" s="25" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E8" s="20" t="n"/>
+      <c r="E8" s="24" t="n"/>
     </row>
     <row r="9" ht="20" customHeight="1">
-      <c r="A9" s="8" t="inlineStr">
+      <c r="A9" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B9" s="7" t="inlineStr">
+      <c r="B9" s="8" t="inlineStr">
         <is>
           <t>食器用洗剤</t>
         </is>
       </c>
-      <c r="C9" s="19" t="inlineStr"/>
-      <c r="D9" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E9" s="20" t="n"/>
+      <c r="C9" s="21" t="inlineStr"/>
+      <c r="D9" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E9" s="24" t="n"/>
     </row>
     <row r="10" ht="20" customHeight="1">
-      <c r="A10" s="8" t="inlineStr">
+      <c r="A10" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B10" s="7" t="inlineStr">
+      <c r="B10" s="8" t="inlineStr">
         <is>
           <t>食器用スポンジ</t>
         </is>
       </c>
-      <c r="C10" s="19" t="inlineStr"/>
-      <c r="D10" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E10" s="20" t="n"/>
+      <c r="C10" s="21" t="inlineStr"/>
+      <c r="D10" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E10" s="24" t="n"/>
     </row>
     <row r="11" ht="20" customHeight="1">
-      <c r="A11" s="8" t="inlineStr">
+      <c r="A11" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B11" s="7" t="inlineStr">
+      <c r="B11" s="8" t="inlineStr">
         <is>
           <t>ボトルブラシ</t>
         </is>
       </c>
-      <c r="C11" s="19" t="inlineStr">
+      <c r="C11" s="21" t="inlineStr">
         <is>
           <t>プロテインシェイカーのこびり付き</t>
         </is>
       </c>
-      <c r="D11" s="21" t="inlineStr">
+      <c r="D11" s="25" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E11" s="20" t="n"/>
+      <c r="E11" s="24" t="n"/>
     </row>
     <row r="12" ht="20" customHeight="1">
-      <c r="A12" s="8" t="inlineStr">
+      <c r="A12" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B12" s="7" t="inlineStr">
+      <c r="B12" s="8" t="inlineStr">
         <is>
           <t>食洗機用洗剤</t>
         </is>
       </c>
-      <c r="C12" s="19" t="inlineStr"/>
-      <c r="D12" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E12" s="20" t="n"/>
+      <c r="C12" s="21" t="inlineStr"/>
+      <c r="D12" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E12" s="24" t="n"/>
     </row>
     <row r="13" ht="20" customHeight="1">
-      <c r="A13" s="8" t="inlineStr">
+      <c r="A13" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B13" s="7" t="inlineStr">
+      <c r="B13" s="8" t="inlineStr">
         <is>
           <t>コンロ用洗剤（油汚れ用）</t>
         </is>
       </c>
-      <c r="C13" s="19" t="inlineStr">
+      <c r="C13" s="21" t="inlineStr">
         <is>
           <t>ガスコンロ・天板</t>
         </is>
       </c>
-      <c r="D13" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E13" s="20" t="n"/>
+      <c r="D13" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E13" s="24" t="n"/>
     </row>
     <row r="14" ht="20" customHeight="1">
-      <c r="A14" s="8" t="inlineStr">
+      <c r="A14" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B14" s="7" t="inlineStr">
+      <c r="B14" s="8" t="inlineStr">
         <is>
           <t>シンク用スポンジ</t>
         </is>
       </c>
-      <c r="C14" s="19" t="inlineStr">
+      <c r="C14" s="21" t="inlineStr">
         <is>
           <t>シンクをこする（食器用とは別にする）</t>
         </is>
       </c>
-      <c r="D14" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E14" s="20" t="n"/>
+      <c r="D14" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E14" s="24" t="n"/>
     </row>
     <row r="15" ht="20" customHeight="1">
-      <c r="A15" s="8" t="inlineStr">
+      <c r="A15" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B15" s="7" t="inlineStr">
+      <c r="B15" s="8" t="inlineStr">
         <is>
           <t>排水口ネット</t>
         </is>
       </c>
-      <c r="C15" s="19" t="inlineStr">
+      <c r="C15" s="21" t="inlineStr">
         <is>
           <t>排水口のゴミ受け</t>
         </is>
       </c>
-      <c r="D15" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E15" s="20" t="n"/>
+      <c r="D15" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E15" s="24" t="n"/>
     </row>
     <row r="16" ht="30" customHeight="1">
-      <c r="A16" s="8" t="inlineStr">
+      <c r="A16" s="9" t="inlineStr">
         <is>
           <t>キッチン</t>
         </is>
       </c>
-      <c r="B16" s="7" t="inlineStr">
+      <c r="B16" s="8" t="inlineStr">
         <is>
           <t>シンク・洗面台用 撥水コート剤</t>
         </is>
       </c>
-      <c r="C16" s="19" t="inlineStr">
+      <c r="C16" s="21" t="inlineStr">
         <is>
           <t>月1回。水回り兼用の物なら1本で両方に使えます</t>
         </is>
       </c>
-      <c r="D16" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E16" s="20" t="n"/>
+      <c r="D16" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E16" s="24" t="n"/>
     </row>
     <row r="17" ht="30" customHeight="1">
-      <c r="A17" s="8" t="inlineStr">
+      <c r="A17" s="9" t="inlineStr">
         <is>
           <t>排水口</t>
         </is>
       </c>
-      <c r="B17" s="7" t="inlineStr">
+      <c r="B17" s="8" t="inlineStr">
         <is>
           <t>パイプユニッシュ</t>
         </is>
       </c>
-      <c r="C17" s="19" t="inlineStr">
+      <c r="C17" s="21" t="inlineStr">
         <is>
           <t>キッチン・お風呂は2週に1回、洗面台は月1回</t>
         </is>
       </c>
-      <c r="D17" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E17" s="20" t="n"/>
+      <c r="D17" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E17" s="24" t="n"/>
     </row>
     <row r="18" ht="20" customHeight="1">
-      <c r="A18" s="8" t="inlineStr">
+      <c r="A18" s="9" t="inlineStr">
         <is>
           <t>トイレ</t>
         </is>
       </c>
-      <c r="B18" s="7" t="inlineStr">
+      <c r="B18" s="8" t="inlineStr">
         <is>
           <t>トイレ用洗剤・トイレブラシ</t>
         </is>
       </c>
-      <c r="C18" s="19" t="inlineStr">
+      <c r="C18" s="21" t="inlineStr">
         <is>
           <t>上の棚</t>
         </is>
       </c>
-      <c r="D18" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E18" s="20" t="n"/>
+      <c r="D18" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E18" s="24" t="n"/>
     </row>
     <row r="19" ht="20" customHeight="1">
-      <c r="A19" s="8" t="inlineStr">
+      <c r="A19" s="9" t="inlineStr">
         <is>
           <t>トイレ</t>
         </is>
       </c>
-      <c r="B19" s="7" t="inlineStr">
+      <c r="B19" s="8" t="inlineStr">
         <is>
           <t>トイレ掃除用シート</t>
         </is>
       </c>
-      <c r="C19" s="19" t="inlineStr">
+      <c r="C19" s="21" t="inlineStr">
         <is>
           <t>便座・床の拭き掃除</t>
         </is>
       </c>
-      <c r="D19" s="21" t="inlineStr">
+      <c r="D19" s="25" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E19" s="20" t="n"/>
+      <c r="E19" s="24" t="n"/>
     </row>
     <row r="20" ht="20" customHeight="1">
-      <c r="A20" s="8" t="inlineStr">
+      <c r="A20" s="9" t="inlineStr">
         <is>
           <t>洗面台</t>
         </is>
       </c>
-      <c r="B20" s="7" t="inlineStr">
+      <c r="B20" s="8" t="inlineStr">
         <is>
           <t>スポンジ（洗面台用）</t>
         </is>
       </c>
-      <c r="C20" s="19" t="inlineStr">
+      <c r="C20" s="21" t="inlineStr">
         <is>
           <t>ボウルをこする</t>
         </is>
       </c>
-      <c r="D20" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E20" s="20" t="n"/>
+      <c r="D20" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E20" s="24" t="n"/>
     </row>
     <row r="21" ht="20" customHeight="1">
-      <c r="A21" s="8" t="inlineStr">
+      <c r="A21" s="9" t="inlineStr">
         <is>
           <t>洗面台・お風呂</t>
         </is>
       </c>
-      <c r="B21" s="7" t="inlineStr">
+      <c r="B21" s="8" t="inlineStr">
         <is>
           <t>排水口用の小さいブラシ</t>
         </is>
       </c>
-      <c r="C21" s="19" t="inlineStr">
+      <c r="C21" s="21" t="inlineStr">
         <is>
           <t>髪の毛・ぬめり取り</t>
         </is>
       </c>
-      <c r="D21" s="21" t="inlineStr">
+      <c r="D21" s="25" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E21" s="20" t="n"/>
+      <c r="E21" s="24" t="n"/>
     </row>
     <row r="22" ht="30" customHeight="1">
-      <c r="A22" s="8" t="inlineStr">
+      <c r="A22" s="9" t="inlineStr">
         <is>
           <t>お風呂</t>
         </is>
       </c>
-      <c r="B22" s="7" t="inlineStr">
+      <c r="B22" s="8" t="inlineStr">
         <is>
           <t>浴槽用スプレー洗剤（30秒で流すタイプ）</t>
         </is>
       </c>
-      <c r="C22" s="19" t="inlineStr">
+      <c r="C22" s="21" t="inlineStr">
         <is>
           <t>使用中の物</t>
         </is>
       </c>
-      <c r="D22" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E22" s="20" t="n"/>
+      <c r="D22" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E22" s="24" t="n"/>
     </row>
     <row r="23" ht="20" customHeight="1">
-      <c r="A23" s="8" t="inlineStr">
+      <c r="A23" s="9" t="inlineStr">
         <is>
           <t>お風呂</t>
         </is>
       </c>
-      <c r="B23" s="7" t="inlineStr">
+      <c r="B23" s="8" t="inlineStr">
         <is>
           <t>浴室用スポンジ・柄つきブラシ</t>
         </is>
       </c>
-      <c r="C23" s="19" t="inlineStr">
+      <c r="C23" s="21" t="inlineStr">
         <is>
           <t>床・壁・椅子・テーブル</t>
         </is>
       </c>
-      <c r="D23" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E23" s="20" t="n"/>
+      <c r="D23" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E23" s="24" t="n"/>
     </row>
     <row r="24" ht="20" customHeight="1">
-      <c r="A24" s="8" t="inlineStr">
+      <c r="A24" s="9" t="inlineStr">
         <is>
           <t>お風呂</t>
         </is>
       </c>
-      <c r="B24" s="7" t="inlineStr">
+      <c r="B24" s="8" t="inlineStr">
         <is>
           <t>防カビくん煙剤</t>
         </is>
       </c>
-      <c r="C24" s="19" t="inlineStr">
+      <c r="C24" s="21" t="inlineStr">
         <is>
           <t>2か月に1回（年6個）</t>
         </is>
       </c>
-      <c r="D24" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E24" s="20" t="n"/>
+      <c r="D24" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E24" s="24" t="n"/>
     </row>
     <row r="25" ht="20" customHeight="1">
-      <c r="A25" s="8" t="inlineStr">
+      <c r="A25" s="9" t="inlineStr">
         <is>
           <t>ホコリ取り</t>
         </is>
       </c>
-      <c r="B25" s="7" t="inlineStr">
+      <c r="B25" s="8" t="inlineStr">
         <is>
           <t>ハンディモップ（替えシートも）</t>
         </is>
       </c>
-      <c r="C25" s="19" t="inlineStr">
+      <c r="C25" s="21" t="inlineStr">
         <is>
           <t>テーブル・ベッドフレーム・台・お風呂の扉</t>
         </is>
       </c>
-      <c r="D25" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E25" s="20" t="n"/>
+      <c r="D25" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E25" s="24" t="n"/>
     </row>
     <row r="26" ht="30" customHeight="1">
-      <c r="A26" s="8" t="inlineStr">
+      <c r="A26" s="9" t="inlineStr">
         <is>
           <t>拭き掃除</t>
         </is>
       </c>
-      <c r="B26" s="7" t="inlineStr">
+      <c r="B26" s="8" t="inlineStr">
         <is>
           <t>マイクロファイバークロス（数枚）</t>
         </is>
       </c>
-      <c r="C26" s="19" t="inlineStr">
+      <c r="C26" s="21" t="inlineStr">
         <is>
           <t>水拭き用・乾拭き用に分ける。ガラスのテーブル・シンク・洗面台</t>
         </is>
       </c>
-      <c r="D26" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E26" s="20" t="n"/>
+      <c r="D26" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E26" s="24" t="n"/>
     </row>
     <row r="27" ht="30" customHeight="1">
-      <c r="A27" s="8" t="inlineStr">
+      <c r="A27" s="9" t="inlineStr">
         <is>
           <t>拭き掃除</t>
         </is>
       </c>
-      <c r="B27" s="7" t="inlineStr">
+      <c r="B27" s="8" t="inlineStr">
         <is>
           <t>ガラス用クリーナー</t>
         </is>
       </c>
-      <c r="C27" s="19" t="inlineStr">
+      <c r="C27" s="21" t="inlineStr">
         <is>
           <t>窓ガラス（季節ごと）。ガラスのテーブルの汚れがひどい時</t>
         </is>
       </c>
-      <c r="D27" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E27" s="20" t="n"/>
+      <c r="D27" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E27" s="24" t="n"/>
     </row>
     <row r="28" ht="20" customHeight="1">
-      <c r="A28" s="8" t="inlineStr">
+      <c r="A28" s="9" t="inlineStr">
         <is>
           <t>窓</t>
         </is>
       </c>
-      <c r="B28" s="7" t="inlineStr">
+      <c r="B28" s="8" t="inlineStr">
         <is>
           <t>網戸用ブラシ（またはスポンジ）</t>
         </is>
       </c>
-      <c r="C28" s="19" t="inlineStr">
+      <c r="C28" s="21" t="inlineStr">
         <is>
           <t>網戸の拭き掃除（季節ごと）</t>
         </is>
       </c>
-      <c r="D28" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E28" s="20" t="n"/>
+      <c r="D28" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E28" s="24" t="n"/>
     </row>
     <row r="29" ht="20" customHeight="1">
-      <c r="A29" s="8" t="inlineStr">
+      <c r="A29" s="9" t="inlineStr">
         <is>
           <t>床</t>
         </is>
       </c>
-      <c r="B29" s="7" t="inlineStr">
+      <c r="B29" s="8" t="inlineStr">
         <is>
           <t>掃除機</t>
         </is>
       </c>
-      <c r="C29" s="19" t="inlineStr">
+      <c r="C29" s="21" t="inlineStr">
         <is>
           <t>部屋と玄関</t>
         </is>
       </c>
-      <c r="D29" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E29" s="20" t="n"/>
+      <c r="D29" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E29" s="24" t="n"/>
     </row>
     <row r="30" ht="30" customHeight="1">
-      <c r="A30" s="8" t="inlineStr">
+      <c r="A30" s="9" t="inlineStr">
         <is>
           <t>床</t>
         </is>
       </c>
-      <c r="B30" s="7" t="inlineStr">
+      <c r="B30" s="8" t="inlineStr">
         <is>
           <t>クイックルワイパー（ウエットシート）</t>
         </is>
       </c>
-      <c r="C30" s="19" t="inlineStr">
+      <c r="C30" s="21" t="inlineStr">
         <is>
           <t>2週に1回</t>
         </is>
       </c>
-      <c r="D30" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E30" s="20" t="n"/>
+      <c r="D30" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E30" s="24" t="n"/>
     </row>
     <row r="31" ht="30" customHeight="1">
-      <c r="A31" s="8" t="inlineStr">
+      <c r="A31" s="9" t="inlineStr">
         <is>
           <t>玄関</t>
         </is>
       </c>
-      <c r="B31" s="7" t="inlineStr">
+      <c r="B31" s="8" t="inlineStr">
         <is>
           <t>靴クリーム（黒用・白用）</t>
         </is>
       </c>
-      <c r="C31" s="19" t="inlineStr">
+      <c r="C31" s="21" t="inlineStr">
         <is>
           <t>月1回の靴磨き。靴の色に合わせて使い分ける</t>
         </is>
       </c>
-      <c r="D31" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E31" s="20" t="n"/>
+      <c r="D31" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E31" s="24" t="n"/>
     </row>
     <row r="32" ht="20" customHeight="1">
-      <c r="A32" s="8" t="inlineStr">
+      <c r="A32" s="9" t="inlineStr">
         <is>
           <t>玄関</t>
         </is>
       </c>
-      <c r="B32" s="7" t="inlineStr">
+      <c r="B32" s="8" t="inlineStr">
         <is>
           <t>靴磨き用ブラシ・布</t>
         </is>
       </c>
-      <c r="C32" s="19" t="inlineStr"/>
-      <c r="D32" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E32" s="20" t="n"/>
+      <c r="C32" s="21" t="inlineStr"/>
+      <c r="D32" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E32" s="24" t="n"/>
     </row>
     <row r="33" ht="20" customHeight="1">
-      <c r="A33" s="8" t="inlineStr">
+      <c r="A33" s="9" t="inlineStr">
         <is>
           <t>消臭</t>
         </is>
       </c>
-      <c r="B33" s="7" t="inlineStr">
+      <c r="B33" s="8" t="inlineStr">
         <is>
           <t>布用消臭スプレー</t>
         </is>
       </c>
-      <c r="C33" s="19" t="inlineStr">
+      <c r="C33" s="21" t="inlineStr">
         <is>
           <t>靴・カーテン・ソファ。毎回</t>
         </is>
       </c>
-      <c r="D33" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E33" s="20" t="n"/>
+      <c r="D33" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E33" s="24" t="n"/>
     </row>
     <row r="34" ht="20" customHeight="1">
-      <c r="A34" s="8" t="inlineStr">
+      <c r="A34" s="9" t="inlineStr">
         <is>
           <t>ゴミ</t>
         </is>
       </c>
-      <c r="B34" s="7" t="inlineStr">
+      <c r="B34" s="8" t="inlineStr">
         <is>
           <t>名古屋市指定ごみ袋（可燃用）</t>
         </is>
       </c>
-      <c r="C34" s="19" t="inlineStr">
+      <c r="C34" s="21" t="inlineStr">
         <is>
           <t>燃えるゴミを出す袋</t>
         </is>
       </c>
-      <c r="D34" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E34" s="20" t="n"/>
+      <c r="D34" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E34" s="24" t="n"/>
     </row>
     <row r="35" ht="20" customHeight="1">
-      <c r="A35" s="8" t="inlineStr">
+      <c r="A35" s="9" t="inlineStr">
         <is>
           <t>ゴミ</t>
         </is>
       </c>
-      <c r="B35" s="7" t="inlineStr">
+      <c r="B35" s="8" t="inlineStr">
         <is>
           <t>ゴミ箱用の袋</t>
         </is>
       </c>
-      <c r="C35" s="19" t="inlineStr">
+      <c r="C35" s="21" t="inlineStr">
         <is>
           <t>袋が付いていないゴミ箱に付ける</t>
         </is>
       </c>
-      <c r="D35" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E35" s="20" t="n"/>
+      <c r="D35" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E35" s="24" t="n"/>
     </row>
     <row r="36" ht="20" customHeight="1">
-      <c r="A36" s="8" t="inlineStr">
+      <c r="A36" s="9" t="inlineStr">
         <is>
           <t>ゴミ</t>
         </is>
       </c>
-      <c r="B36" s="7" t="inlineStr">
+      <c r="B36" s="8" t="inlineStr">
         <is>
           <t>除菌シート</t>
         </is>
       </c>
-      <c r="C36" s="19" t="inlineStr">
+      <c r="C36" s="21" t="inlineStr">
         <is>
           <t>汚れたゴミ箱の中の掃除</t>
         </is>
       </c>
-      <c r="D36" s="21" t="inlineStr">
+      <c r="D36" s="25" t="inlineStr">
         <is>
           <t>あると便利</t>
         </is>
       </c>
-      <c r="E36" s="20" t="n"/>
+      <c r="E36" s="24" t="n"/>
     </row>
     <row r="37" ht="20" customHeight="1">
-      <c r="A37" s="8" t="inlineStr">
+      <c r="A37" s="9" t="inlineStr">
         <is>
           <t>寝室</t>
         </is>
       </c>
-      <c r="B37" s="7" t="inlineStr">
+      <c r="B37" s="8" t="inlineStr">
         <is>
           <t>予備のシーツ・枕カバー</t>
         </is>
       </c>
-      <c r="C37" s="19" t="inlineStr">
+      <c r="C37" s="21" t="inlineStr">
         <is>
           <t>シーツ類を洗う週に交換する（予備あり）</t>
         </is>
       </c>
-      <c r="D37" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E37" s="20" t="n"/>
+      <c r="D37" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E37" s="24" t="n"/>
     </row>
     <row r="38" ht="20" customHeight="1">
-      <c r="A38" s="8" t="inlineStr">
+      <c r="A38" s="9" t="inlineStr">
         <is>
           <t>共通</t>
         </is>
       </c>
-      <c r="B38" s="7" t="inlineStr">
+      <c r="B38" s="8" t="inlineStr">
         <is>
           <t>ゴム手袋・使い捨て手袋</t>
         </is>
       </c>
-      <c r="C38" s="19" t="inlineStr">
+      <c r="C38" s="21" t="inlineStr">
         <is>
           <t>トイレ・お風呂・排水口・ゴミ箱</t>
         </is>
       </c>
-      <c r="D38" s="20" t="inlineStr">
-        <is>
-          <t>必須</t>
-        </is>
-      </c>
-      <c r="E38" s="20" t="n"/>
+      <c r="D38" s="24" t="inlineStr">
+        <is>
+          <t>必須</t>
+        </is>
+      </c>
+      <c r="E38" s="24" t="n"/>
     </row>
     <row r="39">
-      <c r="A39" s="11" t="inlineStr">
+      <c r="A39" s="12" t="inlineStr">
         <is>
           <t>※パイプユニッシュ（塩素系）と酸性の洗剤（クエン酸など）は、同じ場所に置かず、混ぜないでください。</t>
         </is>
